--- a/02_Dataset_EDA_Feature_UMAP_Mahalanobis/"distance" from new FeCrNiCoV data
to hardness dataset.xlsx
+++ b/02_Dataset_EDA_Feature_UMAP_Mahalanobis/"distance" from new FeCrNiCoV data
to hardness dataset.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,178 +425,178 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF70"/>
+  <dimension ref="A1:AE70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cr</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Cr</t>
+          <t>Ni</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Ni</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>W</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>Nb</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Nb</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>V</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Ta</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Ta</t>
+          <t>Ti</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Ti</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Zr</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Zr</t>
+          <t>Hf</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Hf</t>
+          <t>delta_a</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>delta_a</t>
+          <t>Tm</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Tm</t>
+          <t>sigma_Tm</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>sigma_Tm</t>
+          <t>Hmix</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Hmix</t>
+          <t>sigma_Hmix</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>sigma_Hmix</t>
+          <t>sigma_elec_nega</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>sigma_elec_nega</t>
+          <t>VEC</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>VEC</t>
+          <t>sigma_VEC</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sigma_VEC</t>
+          <t>Mahalanobis</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Mahalanobis</t>
+          <t>p value</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>p value</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>UMAP Component 1</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>UMAP Component 1</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>UMAP Component 2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>680</v>
+      <c r="A2" t="n">
+        <v>10.27148578895017</v>
       </c>
       <c r="B2" t="n">
-        <v>10.27148578895017</v>
+        <v>31.29049408631733</v>
       </c>
       <c r="C2" t="n">
-        <v>31.29049408631733</v>
+        <v>51.98555612171399</v>
       </c>
       <c r="D2" t="n">
-        <v>51.98555612171399</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -620,19 +620,19 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.601017748048015</v>
       </c>
       <c r="M2" t="n">
-        <v>1.601017748048015</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.851446254970497</v>
       </c>
       <c r="P2" t="n">
-        <v>4.851446254970497</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -641,62 +641,59 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>0.007567560866934837</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007567560866934837</v>
+        <v>1898.775788633536</v>
       </c>
       <c r="U2" t="n">
-        <v>1898.775788633536</v>
+        <v>210.08295698605</v>
       </c>
       <c r="V2" t="n">
-        <v>210.08295698605</v>
+        <v>-6.271298853023574</v>
       </c>
       <c r="W2" t="n">
-        <v>-6.271298853023574</v>
+        <v>2.111357319910797</v>
       </c>
       <c r="X2" t="n">
-        <v>2.111357319910797</v>
+        <v>0.1156826189583638</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1156826189583638</v>
+        <v>8.311398201392562</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.311398201392562</v>
+        <v>1.854883648133144</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.854883648133144</v>
+        <v>24.32812752921359</v>
       </c>
       <c r="AB2" t="n">
-        <v>24.32812751248733</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>5.214518746909924e-06</v>
-      </c>
-      <c r="AD2" t="inlineStr">
+        <v>5.214518703278159e-06</v>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD2" t="n">
+        <v>2.671647787094116</v>
+      </c>
       <c r="AE2" t="n">
-        <v>1.448436975479126</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>5.986886978149414</v>
+        <v>6.017104148864746</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>681</v>
+      <c r="A3" t="n">
+        <v>10.49540628405087</v>
       </c>
       <c r="B3" t="n">
-        <v>10.49540628405087</v>
+        <v>32.94577234077189</v>
       </c>
       <c r="C3" t="n">
-        <v>32.94577234077189</v>
+        <v>47.58971794791144</v>
       </c>
       <c r="D3" t="n">
-        <v>47.58971794791144</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -720,19 +717,19 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.334196184849361</v>
       </c>
       <c r="M3" t="n">
-        <v>2.334196184849361</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>6.634907242416435</v>
       </c>
       <c r="P3" t="n">
-        <v>6.634907242416435</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -741,62 +738,59 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.008981693372021508</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008981693372021508</v>
+        <v>1910.795152973678</v>
       </c>
       <c r="U3" t="n">
-        <v>1910.795152973678</v>
+        <v>212.1178454432332</v>
       </c>
       <c r="V3" t="n">
-        <v>212.1178454432332</v>
+        <v>-6.468448355120914</v>
       </c>
       <c r="W3" t="n">
-        <v>-6.468448355120914</v>
+        <v>2.332729780166001</v>
       </c>
       <c r="X3" t="n">
-        <v>2.332729780166001</v>
+        <v>0.1167603319357038</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1167603319357038</v>
+        <v>8.184012913062192</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.184012913062192</v>
+        <v>1.86699756583838</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.86699756583838</v>
+        <v>24.35820499484201</v>
       </c>
       <c r="AB3" t="n">
-        <v>24.35820498044416</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>5.136685708673205e-06</v>
-      </c>
-      <c r="AD3" t="inlineStr">
+        <v>5.136685671702779e-06</v>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD3" t="n">
+        <v>2.821423768997192</v>
+      </c>
       <c r="AE3" t="n">
-        <v>1.565544843673706</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>6.153024196624756</v>
+        <v>6.130617618560791</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>682</v>
+      <c r="A4" t="n">
+        <v>11.11292799977388</v>
       </c>
       <c r="B4" t="n">
-        <v>11.11292799977388</v>
+        <v>32.81214789008236</v>
       </c>
       <c r="C4" t="n">
-        <v>32.81214789008236</v>
+        <v>43.56230343162476</v>
       </c>
       <c r="D4" t="n">
-        <v>43.56230343162476</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -820,19 +814,19 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.278592219785826</v>
       </c>
       <c r="M4" t="n">
-        <v>3.278592219785826</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>9.234028458733178</v>
       </c>
       <c r="P4" t="n">
-        <v>9.234028458733178</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -841,62 +835,59 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.01049891504989097</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01049891504989097</v>
+        <v>1916.090626733144</v>
       </c>
       <c r="U4" t="n">
-        <v>1916.090626733144</v>
+        <v>211.7767346850572</v>
       </c>
       <c r="V4" t="n">
-        <v>211.7767346850572</v>
+        <v>-6.589870748179617</v>
       </c>
       <c r="W4" t="n">
-        <v>-6.589870748179617</v>
+        <v>2.581555258790369</v>
       </c>
       <c r="X4" t="n">
-        <v>2.581555258790369</v>
+        <v>0.1166235588699299</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1166235588699299</v>
+        <v>8.103673917714687</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.103673917714687</v>
+        <v>1.860835719820994</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.860835719820994</v>
+        <v>22.43773221044603</v>
       </c>
       <c r="AB4" t="n">
-        <v>22.43773220089029</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.341863560400114e-05</v>
-      </c>
-      <c r="AD4" t="inlineStr">
+        <v>1.341863553983025e-05</v>
+      </c>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD4" t="n">
+        <v>2.932285070419312</v>
+      </c>
       <c r="AE4" t="n">
-        <v>1.407618999481201</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>6.222729682922363</v>
+        <v>6.229489326477051</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>683</v>
+      <c r="A5" t="n">
+        <v>11.33579528302992</v>
       </c>
       <c r="B5" t="n">
-        <v>11.33579528302992</v>
+        <v>32.22397566351926</v>
       </c>
       <c r="C5" t="n">
-        <v>32.22397566351926</v>
+        <v>39.22125295817604</v>
       </c>
       <c r="D5" t="n">
-        <v>39.22125295817604</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -920,19 +911,19 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4.621174438767964</v>
       </c>
       <c r="M5" t="n">
-        <v>4.621174438767964</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>12.59780165650682</v>
       </c>
       <c r="P5" t="n">
-        <v>12.59780165650682</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -941,62 +932,59 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.01226566696882826</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01226566696882826</v>
+        <v>1921.152628589558</v>
       </c>
       <c r="U5" t="n">
-        <v>1921.152628589558</v>
+        <v>211.2849915172502</v>
       </c>
       <c r="V5" t="n">
-        <v>211.2849915172502</v>
+        <v>-6.791480312375179</v>
       </c>
       <c r="W5" t="n">
-        <v>-6.791480312375179</v>
+        <v>2.858632230826806</v>
       </c>
       <c r="X5" t="n">
-        <v>2.858632230826806</v>
+        <v>0.1165478370541643</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1165478370541643</v>
+        <v>8.021515930217278</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.021515930217278</v>
+        <v>1.855466976740344</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.855466976740344</v>
+        <v>20.90959514240374</v>
       </c>
       <c r="AB5" t="n">
-        <v>20.90959513560961</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.880972460839182e-05</v>
-      </c>
-      <c r="AD5" t="inlineStr">
+        <v>2.880972451047015e-05</v>
+      </c>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD5" t="n">
+        <v>2.928176641464233</v>
+      </c>
       <c r="AE5" t="n">
-        <v>1.482919692993164</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>6.477166175842285</v>
+        <v>6.383233547210693</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>684</v>
+      <c r="A6" t="n">
+        <v>11.53221857575777</v>
       </c>
       <c r="B6" t="n">
-        <v>11.53221857575777</v>
+        <v>30.53157810614559</v>
       </c>
       <c r="C6" t="n">
-        <v>30.53157810614559</v>
+        <v>34.88574415625551</v>
       </c>
       <c r="D6" t="n">
-        <v>34.88574415625551</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1020,19 +1008,19 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>6.330070586728944</v>
       </c>
       <c r="M6" t="n">
-        <v>6.330070586728944</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>16.72038857511217</v>
       </c>
       <c r="P6" t="n">
-        <v>16.72038857511217</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1041,62 +1029,59 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.01411476619079386</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01411476619079386</v>
+        <v>1923.115521791667</v>
       </c>
       <c r="U6" t="n">
-        <v>1923.115521791667</v>
+        <v>209.9806668056275</v>
       </c>
       <c r="V6" t="n">
-        <v>209.9806668056275</v>
+        <v>-7.047384736419096</v>
       </c>
       <c r="W6" t="n">
-        <v>-7.047384736419096</v>
+        <v>3.152087504220492</v>
       </c>
       <c r="X6" t="n">
-        <v>3.152087504220492</v>
+        <v>0.1161926678246368</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1161926678246368</v>
+        <v>7.958413700411956</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.958413700411956</v>
+        <v>1.846723059137253</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.846723059137253</v>
+        <v>19.22169757226645</v>
       </c>
       <c r="AB6" t="n">
-        <v>19.2216975668602</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>6.699793342646032e-05</v>
-      </c>
-      <c r="AD6" t="inlineStr">
+        <v>6.699793324538295e-05</v>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD6" t="n">
+        <v>2.823781251907349</v>
+      </c>
       <c r="AE6" t="n">
-        <v>1.42179548740387</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>6.632607460021973</v>
+        <v>6.490841388702393</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>685</v>
+      <c r="A7" t="n">
+        <v>11.73836346032553</v>
       </c>
       <c r="B7" t="n">
-        <v>11.73836346032553</v>
+        <v>22.86895992276621</v>
       </c>
       <c r="C7" t="n">
-        <v>22.86895992276621</v>
+        <v>61.37440160498019</v>
       </c>
       <c r="D7" t="n">
-        <v>61.37440160498019</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1120,19 +1105,19 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.259725905661516</v>
       </c>
       <c r="M7" t="n">
-        <v>1.259725905661516</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.758549106266543</v>
       </c>
       <c r="P7" t="n">
-        <v>2.758549106266543</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1141,62 +1126,59 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.006842825225855346</v>
       </c>
       <c r="T7" t="n">
-        <v>0.006842825225855346</v>
+        <v>1857.789691124599</v>
       </c>
       <c r="U7" t="n">
-        <v>1857.789691124599</v>
+        <v>194.3177838840969</v>
       </c>
       <c r="V7" t="n">
-        <v>194.3177838840969</v>
+        <v>-5.614142960297702</v>
       </c>
       <c r="W7" t="n">
-        <v>-5.614142960297702</v>
+        <v>1.937899557480049</v>
       </c>
       <c r="X7" t="n">
-        <v>1.937899557480049</v>
+        <v>0.107669417748325</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.107669417748325</v>
+        <v>8.670169506141644</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.670169506141644</v>
+        <v>1.750890315651342</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.750890315651342</v>
+        <v>21.72049145767553</v>
       </c>
       <c r="AB7" t="n">
-        <v>21.72049143967628</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.920680874156755e-05</v>
-      </c>
-      <c r="AD7" t="inlineStr">
+        <v>1.920680856870582e-05</v>
+      </c>
+      <c r="AC7" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD7" t="n">
+        <v>2.224638938903809</v>
+      </c>
       <c r="AE7" t="n">
-        <v>0.9697780013084412</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>5.618061542510986</v>
+        <v>5.720539569854736</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>686</v>
+      <c r="A8" t="n">
+        <v>12.47588443056982</v>
       </c>
       <c r="B8" t="n">
-        <v>12.47588443056982</v>
+        <v>24.98368892830287</v>
       </c>
       <c r="C8" t="n">
-        <v>24.98368892830287</v>
+        <v>56.71556632861048</v>
       </c>
       <c r="D8" t="n">
-        <v>56.71556632861048</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1220,19 +1202,19 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.634808196102548</v>
       </c>
       <c r="M8" t="n">
-        <v>1.634808196102548</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.190052116414273</v>
       </c>
       <c r="P8" t="n">
-        <v>4.190052116414273</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1241,62 +1223,59 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.007710236189675343</v>
       </c>
       <c r="T8" t="n">
-        <v>0.007710236189675343</v>
+        <v>1870.760523351667</v>
       </c>
       <c r="U8" t="n">
-        <v>1870.760523351667</v>
+        <v>199.1305171658607</v>
       </c>
       <c r="V8" t="n">
-        <v>199.1305171658607</v>
+        <v>-5.867117265857988</v>
       </c>
       <c r="W8" t="n">
-        <v>-5.867117265857988</v>
+        <v>2.123633445264106</v>
       </c>
       <c r="X8" t="n">
-        <v>2.123633445264106</v>
+        <v>0.1101136944012719</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1101136944012719</v>
+        <v>8.533698013821583</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.533698013821583</v>
+        <v>1.783668816170993</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.783668816170993</v>
+        <v>19.10912146360958</v>
       </c>
       <c r="AB8" t="n">
-        <v>19.10912144847112</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>7.087727311683167e-05</v>
-      </c>
-      <c r="AD8" t="inlineStr">
+        <v>7.087727258037191e-05</v>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD8" t="n">
+        <v>2.427322387695312</v>
+      </c>
       <c r="AE8" t="n">
-        <v>1.265334844589233</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>5.840639114379883</v>
+        <v>5.986257553100586</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>687</v>
+      <c r="A9" t="n">
+        <v>13.31360035996819</v>
       </c>
       <c r="B9" t="n">
-        <v>13.31360035996819</v>
+        <v>26.54966770489246</v>
       </c>
       <c r="C9" t="n">
-        <v>26.54966770489246</v>
+        <v>52.00259710594798</v>
       </c>
       <c r="D9" t="n">
-        <v>52.00259710594798</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1320,19 +1299,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.419855387591513</v>
       </c>
       <c r="M9" t="n">
-        <v>2.419855387591513</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>5.714279441599858</v>
       </c>
       <c r="P9" t="n">
-        <v>5.714279441599858</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1341,62 +1320,59 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.009226486237911845</v>
       </c>
       <c r="T9" t="n">
-        <v>0.009226486237911845</v>
+        <v>1883.143030122693</v>
       </c>
       <c r="U9" t="n">
-        <v>1883.143030122693</v>
+        <v>202.7080861624065</v>
       </c>
       <c r="V9" t="n">
-        <v>202.7080861624065</v>
+        <v>-6.166938979389202</v>
       </c>
       <c r="W9" t="n">
-        <v>-6.166938979389202</v>
+        <v>2.381082478348045</v>
       </c>
       <c r="X9" t="n">
-        <v>2.381082478348045</v>
+        <v>0.1120245704843556</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1120245704843556</v>
+        <v>8.396325744972188</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.396325744972188</v>
+        <v>1.810259609945069</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.810259609945069</v>
+        <v>17.22568069989993</v>
       </c>
       <c r="AB9" t="n">
-        <v>17.22568068796729</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.0001817569243647288</v>
-      </c>
-      <c r="AD9" t="inlineStr">
+        <v>0.0001817569232802629</v>
+      </c>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD9" t="n">
+        <v>2.516836404800415</v>
+      </c>
       <c r="AE9" t="n">
-        <v>1.287466049194336</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>6.06306791305542</v>
+        <v>6.056132316589355</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>688</v>
+      <c r="A10" t="n">
+        <v>14.04586286313179</v>
       </c>
       <c r="B10" t="n">
-        <v>14.04586286313179</v>
+        <v>26.99036608992429</v>
       </c>
       <c r="C10" t="n">
-        <v>26.99036608992429</v>
+        <v>46.90426102417226</v>
       </c>
       <c r="D10" t="n">
-        <v>46.90426102417226</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1420,19 +1396,19 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.607507573809785</v>
       </c>
       <c r="M10" t="n">
-        <v>3.607507573809785</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>8.452002448961867</v>
       </c>
       <c r="P10" t="n">
-        <v>8.452002448961867</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1441,62 +1417,59 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.01107494595998307</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01107494595998307</v>
+        <v>1892.497595706803</v>
       </c>
       <c r="U10" t="n">
-        <v>1892.497595706803</v>
+        <v>204.2175852139688</v>
       </c>
       <c r="V10" t="n">
-        <v>204.2175852139688</v>
+        <v>-6.446623242846035</v>
       </c>
       <c r="W10" t="n">
-        <v>-6.446623242846035</v>
+        <v>2.695215082590741</v>
       </c>
       <c r="X10" t="n">
-        <v>2.695215082590741</v>
+        <v>0.1129461844622978</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1129461844622978</v>
+        <v>8.275277740967283</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.275277740967283</v>
+        <v>1.821423299585024</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.821423299585024</v>
+        <v>15.1648108919939</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.16481088503465</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.0005093345732500865</v>
-      </c>
-      <c r="AD10" t="inlineStr">
+        <v>0.0005093345714778375</v>
+      </c>
+      <c r="AC10" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD10" t="n">
+        <v>2.657833337783813</v>
+      </c>
       <c r="AE10" t="n">
-        <v>1.217727303504944</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>6.189106464385986</v>
+        <v>6.233531951904297</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>689</v>
+      <c r="A11" t="n">
+        <v>14.78596965177877</v>
       </c>
       <c r="B11" t="n">
-        <v>14.78596965177877</v>
+        <v>27.06870998804106</v>
       </c>
       <c r="C11" t="n">
-        <v>27.06870998804106</v>
+        <v>42.00036448179262</v>
       </c>
       <c r="D11" t="n">
-        <v>42.00036448179262</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1520,19 +1493,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>5.28571231605495</v>
       </c>
       <c r="M11" t="n">
-        <v>5.28571231605495</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>10.8592435623326</v>
       </c>
       <c r="P11" t="n">
-        <v>10.8592435623326</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1541,62 +1514,59 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.01316040153308272</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01316040153308272</v>
+        <v>1902.325520402011</v>
       </c>
       <c r="U11" t="n">
-        <v>1902.325520402011</v>
+        <v>205.5594757974689</v>
       </c>
       <c r="V11" t="n">
-        <v>205.5594757974689</v>
+        <v>-6.825920157494785</v>
       </c>
       <c r="W11" t="n">
-        <v>-6.825920157494785</v>
+        <v>3.019598288428964</v>
       </c>
       <c r="X11" t="n">
-        <v>3.019598288428964</v>
+        <v>0.1139088323443737</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1139088323443737</v>
+        <v>8.147005641274992</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.147005641274992</v>
+        <v>1.835044455810978</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.835044455810978</v>
+        <v>14.28927492518501</v>
       </c>
       <c r="AB11" t="n">
-        <v>14.28927491605369</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.0007890842532013442</v>
-      </c>
-      <c r="AD11" t="inlineStr">
+        <v>0.0007890842495986705</v>
+      </c>
+      <c r="AC11" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD11" t="n">
+        <v>2.737283706665039</v>
+      </c>
       <c r="AE11" t="n">
-        <v>1.363960266113281</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>6.530431747436523</v>
+        <v>6.358973026275635</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>690</v>
+      <c r="A12" t="n">
+        <v>14.60750023008277</v>
       </c>
       <c r="B12" t="n">
-        <v>14.60750023008277</v>
+        <v>25.99044553565464</v>
       </c>
       <c r="C12" t="n">
-        <v>25.99044553565464</v>
+        <v>37.75047907645035</v>
       </c>
       <c r="D12" t="n">
-        <v>37.75047907645035</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1620,19 +1590,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>7.292177963267194</v>
       </c>
       <c r="M12" t="n">
-        <v>7.292177963267194</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>14.35939719454503</v>
       </c>
       <c r="P12" t="n">
-        <v>14.35939719454503</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1641,62 +1611,59 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.01515838317678847</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01515838317678847</v>
+        <v>1908.03799361034</v>
       </c>
       <c r="U12" t="n">
-        <v>1908.03799361034</v>
+        <v>205.813236893549</v>
       </c>
       <c r="V12" t="n">
-        <v>205.813236893549</v>
+        <v>-7.253456385052127</v>
       </c>
       <c r="W12" t="n">
-        <v>-7.253456385052127</v>
+        <v>3.349368283476078</v>
       </c>
       <c r="X12" t="n">
-        <v>3.349368283476078</v>
+        <v>0.1145428712332797</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1145428712332797</v>
+        <v>8.056311680113808</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.056311680113808</v>
+        <v>1.845065614118694</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.845065614118694</v>
+        <v>13.86207773951257</v>
       </c>
       <c r="AB12" t="n">
-        <v>13.86207773711803</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0.0009769853816125051</v>
-      </c>
-      <c r="AD12" t="inlineStr">
+        <v>0.0009769853804427742</v>
+      </c>
+      <c r="AC12" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD12" t="n">
+        <v>2.805438756942749</v>
+      </c>
       <c r="AE12" t="n">
-        <v>1.320677518844604</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>6.827459335327148</v>
+        <v>6.565057277679443</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>691</v>
+      <c r="A13" t="n">
+        <v>13.93632017907879</v>
       </c>
       <c r="B13" t="n">
-        <v>13.93632017907879</v>
+        <v>24.36465676002593</v>
       </c>
       <c r="C13" t="n">
-        <v>24.36465676002593</v>
+        <v>32.8770530221699</v>
       </c>
       <c r="D13" t="n">
-        <v>32.8770530221699</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1720,19 +1687,19 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>10.51764696301523</v>
       </c>
       <c r="M13" t="n">
-        <v>10.51764696301523</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>18.30432307571014</v>
       </c>
       <c r="P13" t="n">
-        <v>18.30432307571014</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1741,62 +1708,59 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.01768471927353749</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01768471927353749</v>
+        <v>1916.753430268094</v>
       </c>
       <c r="U13" t="n">
-        <v>1916.753430268094</v>
+        <v>206.7304620179058</v>
       </c>
       <c r="V13" t="n">
-        <v>206.7304620179058</v>
+        <v>-7.97594706331502</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.97594706331502</v>
+        <v>3.758173114708101</v>
       </c>
       <c r="X13" t="n">
-        <v>3.758173114708101</v>
+        <v>0.1158984378599376</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1158984378599376</v>
+        <v>7.930006739875208</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.930006739875208</v>
+        <v>1.86951759811025</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.86951759811025</v>
+        <v>15.64698007681176</v>
       </c>
       <c r="AB13" t="n">
-        <v>15.64698007292835</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.0004002224515897712</v>
-      </c>
-      <c r="AD13" t="inlineStr">
+        <v>0.0004002224508127261</v>
+      </c>
+      <c r="AC13" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD13" t="n">
+        <v>2.694061517715454</v>
+      </c>
       <c r="AE13" t="n">
-        <v>1.240376830101013</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>7.127925395965576</v>
+        <v>6.893543243408203</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>692</v>
+      <c r="A14" t="n">
+        <v>13.2060787967079</v>
       </c>
       <c r="B14" t="n">
-        <v>13.2060787967079</v>
+        <v>15.02832349645654</v>
       </c>
       <c r="C14" t="n">
-        <v>15.02832349645654</v>
+        <v>69.29549240142492</v>
       </c>
       <c r="D14" t="n">
-        <v>69.29549240142492</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1820,19 +1784,19 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.7977467951202381</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7977467951202381</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.672358510290382</v>
       </c>
       <c r="P14" t="n">
-        <v>1.672358510290382</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1841,62 +1805,59 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>0.005606114639837781</v>
       </c>
       <c r="T14" t="n">
-        <v>0.005606114639837781</v>
+        <v>1818.578263959326</v>
       </c>
       <c r="U14" t="n">
-        <v>1818.578263959326</v>
+        <v>168.3561060540251</v>
       </c>
       <c r="V14" t="n">
-        <v>168.3561060540251</v>
+        <v>-4.477646392720541</v>
       </c>
       <c r="W14" t="n">
-        <v>-4.477646392720541</v>
+        <v>1.708256677610854</v>
       </c>
       <c r="X14" t="n">
-        <v>1.708256677610854</v>
+        <v>0.09416825360061813</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.09416825360061813</v>
+        <v>9.008251048490905</v>
       </c>
       <c r="Z14" t="n">
-        <v>9.008251048490905</v>
+        <v>1.561750253790709</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.561750253790709</v>
+        <v>27.85972301636968</v>
       </c>
       <c r="AB14" t="n">
-        <v>27.85972299059101</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8.919448841737676e-07</v>
-      </c>
-      <c r="AD14" t="inlineStr">
+        <v>8.919448727384705e-07</v>
+      </c>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD14" t="n">
+        <v>1.897273182868958</v>
+      </c>
       <c r="AE14" t="n">
-        <v>0.1595151871442795</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>4.566577911376953</v>
+        <v>4.899761199951172</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>693</v>
+      <c r="A15" t="n">
+        <v>14.43724685121477</v>
       </c>
       <c r="B15" t="n">
-        <v>14.43724685121477</v>
+        <v>17.46573593468872</v>
       </c>
       <c r="C15" t="n">
-        <v>17.46573593468872</v>
+        <v>64.41049102823393</v>
       </c>
       <c r="D15" t="n">
-        <v>64.41049102823393</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1920,19 +1881,19 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.20945092086888</v>
       </c>
       <c r="M15" t="n">
-        <v>1.20945092086888</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.47707526499368</v>
       </c>
       <c r="P15" t="n">
-        <v>2.47707526499368</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1941,62 +1902,59 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.006775170565409099</v>
       </c>
       <c r="T15" t="n">
-        <v>0.006775170565409099</v>
+        <v>1833.694548174602</v>
       </c>
       <c r="U15" t="n">
-        <v>1833.694548174602</v>
+        <v>178.1069290323834</v>
       </c>
       <c r="V15" t="n">
-        <v>178.1069290323834</v>
+        <v>-4.977123927951482</v>
       </c>
       <c r="W15" t="n">
-        <v>-4.977123927951482</v>
+        <v>1.914281381179299</v>
       </c>
       <c r="X15" t="n">
-        <v>1.914281381179299</v>
+        <v>0.09932146237195352</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.09932146237195352</v>
+        <v>8.84991430272982</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.84991430272982</v>
+        <v>1.638625076837699</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.638625076837699</v>
+        <v>21.28809845215243</v>
       </c>
       <c r="AB15" t="n">
-        <v>21.28809843392365</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.384230064256254e-05</v>
-      </c>
-      <c r="AD15" t="inlineStr">
+        <v>2.384230042518087e-05</v>
+      </c>
+      <c r="AC15" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD15" t="n">
+        <v>1.747141480445862</v>
+      </c>
       <c r="AE15" t="n">
-        <v>0.5772117972373962</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>5.229785442352295</v>
+        <v>5.424031257629395</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>694</v>
+      <c r="A16" t="n">
+        <v>15.77509757365795</v>
       </c>
       <c r="B16" t="n">
-        <v>15.77509757365795</v>
+        <v>19.46141471946138</v>
       </c>
       <c r="C16" t="n">
-        <v>19.46141471946138</v>
+        <v>59.47972292144197</v>
       </c>
       <c r="D16" t="n">
-        <v>59.47972292144197</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -2020,19 +1978,19 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.735788529393408</v>
       </c>
       <c r="M16" t="n">
-        <v>1.735788529393408</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.547976256045292</v>
       </c>
       <c r="P16" t="n">
-        <v>3.547976256045292</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2041,62 +1999,59 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.007998684130288678</v>
       </c>
       <c r="T16" t="n">
-        <v>0.007998684130288678</v>
+        <v>1847.320697703437</v>
       </c>
       <c r="U16" t="n">
-        <v>1847.320697703437</v>
+        <v>185.0846877967935</v>
       </c>
       <c r="V16" t="n">
-        <v>185.0846877967935</v>
+        <v>-5.375273100435933</v>
       </c>
       <c r="W16" t="n">
-        <v>-5.375273100435933</v>
+        <v>2.139010897796586</v>
       </c>
       <c r="X16" t="n">
-        <v>2.139010897796586</v>
+        <v>0.1029770967576714</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1029770967576714</v>
+        <v>8.700625057938989</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.700625057938989</v>
+        <v>1.692022026540553</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.692022026540553</v>
+        <v>16.5395153694118</v>
       </c>
       <c r="AB16" t="n">
-        <v>16.53951535339911</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0.0002561473542094239</v>
-      </c>
-      <c r="AD16" t="inlineStr">
+        <v>0.0002561473521586199</v>
+      </c>
+      <c r="AC16" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD16" t="n">
+        <v>1.959473013877869</v>
+      </c>
       <c r="AE16" t="n">
-        <v>0.8253679275512695</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>5.610726833343506</v>
+        <v>5.72845458984375</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>695</v>
+      <c r="A17" t="n">
+        <v>17.01643502058164</v>
       </c>
       <c r="B17" t="n">
-        <v>17.01643502058164</v>
+        <v>21.27838133381189</v>
       </c>
       <c r="C17" t="n">
-        <v>21.27838133381189</v>
+        <v>53.96503504675589</v>
       </c>
       <c r="D17" t="n">
-        <v>53.96503504675589</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -2120,19 +2075,19 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.770549678121697</v>
       </c>
       <c r="M17" t="n">
-        <v>2.770549678121697</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.96959892072887</v>
       </c>
       <c r="P17" t="n">
-        <v>4.96959892072887</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -2141,62 +2096,59 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.009910355224525562</v>
       </c>
       <c r="T17" t="n">
-        <v>0.009910355224525562</v>
+        <v>1862.519712760652</v>
       </c>
       <c r="U17" t="n">
-        <v>1862.519712760652</v>
+        <v>191.5692950747122</v>
       </c>
       <c r="V17" t="n">
-        <v>191.5692950747122</v>
+        <v>-5.868722452599634</v>
       </c>
       <c r="W17" t="n">
-        <v>-5.868722452599634</v>
+        <v>2.462800168495763</v>
       </c>
       <c r="X17" t="n">
-        <v>2.462800168495763</v>
+        <v>0.1064838084249622</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1064838084249622</v>
+        <v>8.53134573047033</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.53134573047033</v>
+        <v>1.743724699764247</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.743724699764247</v>
+        <v>13.0676630695941</v>
       </c>
       <c r="AB17" t="n">
-        <v>13.06766306028684</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0.00145342632078671</v>
-      </c>
-      <c r="AD17" t="inlineStr">
+        <v>0.00145342631402301</v>
+      </c>
+      <c r="AC17" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD17" t="n">
+        <v>2.158027172088623</v>
+      </c>
       <c r="AE17" t="n">
-        <v>0.9739424586296082</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>5.868922710418701</v>
+        <v>5.9543776512146</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>696</v>
+      <c r="A18" t="n">
+        <v>17.57324774662381</v>
       </c>
       <c r="B18" t="n">
-        <v>17.57324774662381</v>
+        <v>21.9085475462501</v>
       </c>
       <c r="C18" t="n">
-        <v>21.9085475462501</v>
+        <v>50.2956906832617</v>
       </c>
       <c r="D18" t="n">
-        <v>50.2956906832617</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -2220,19 +2172,19 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.69510141148884</v>
       </c>
       <c r="M18" t="n">
-        <v>3.69510141148884</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>6.527412612375554</v>
       </c>
       <c r="P18" t="n">
-        <v>6.527412612375554</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2241,62 +2193,59 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.01130136048272857</v>
       </c>
       <c r="T18" t="n">
-        <v>0.01130136048272857</v>
+        <v>1870.999245485742</v>
       </c>
       <c r="U18" t="n">
-        <v>1870.999245485742</v>
+        <v>194.3943070618537</v>
       </c>
       <c r="V18" t="n">
-        <v>194.3943070618537</v>
+        <v>-6.178137385674443</v>
       </c>
       <c r="W18" t="n">
-        <v>-6.178137385674443</v>
+        <v>2.700707230990515</v>
       </c>
       <c r="X18" t="n">
-        <v>2.700707230990515</v>
+        <v>0.1081036941567561</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1081036941567561</v>
+        <v>8.430292685673122</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.430292685673122</v>
+        <v>1.76729345111992</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.76729345111992</v>
+        <v>11.43252661942271</v>
       </c>
       <c r="AB18" t="n">
-        <v>11.43252660951974</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0.003291989108131332</v>
-      </c>
-      <c r="AD18" t="inlineStr">
+        <v>0.003291989091831038</v>
+      </c>
+      <c r="AC18" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD18" t="n">
+        <v>2.196089029312134</v>
+      </c>
       <c r="AE18" t="n">
-        <v>1.018189072608948</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>6.220582008361816</v>
+        <v>6.252355575561523</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>697</v>
+      <c r="A19" t="n">
+        <v>18.2282289394109</v>
       </c>
       <c r="B19" t="n">
-        <v>18.2282289394109</v>
+        <v>22.25825438399324</v>
       </c>
       <c r="C19" t="n">
-        <v>22.25825438399324</v>
+        <v>44.49254902780563</v>
       </c>
       <c r="D19" t="n">
-        <v>44.49254902780563</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2320,19 +2269,19 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>5.896923790443918</v>
       </c>
       <c r="M19" t="n">
-        <v>5.896923790443918</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>9.124043858346317</v>
       </c>
       <c r="P19" t="n">
-        <v>9.124043858346317</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2341,62 +2290,59 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.01394268369701949</v>
       </c>
       <c r="T19" t="n">
-        <v>0.01394268369701949</v>
+        <v>1884.717007471835</v>
       </c>
       <c r="U19" t="n">
-        <v>1884.717007471835</v>
+        <v>198.3108264298762</v>
       </c>
       <c r="V19" t="n">
-        <v>198.3108264298762</v>
+        <v>-6.813358329002254</v>
       </c>
       <c r="W19" t="n">
-        <v>-6.813358329002254</v>
+        <v>3.132689075639008</v>
       </c>
       <c r="X19" t="n">
-        <v>3.132689075639008</v>
+        <v>0.1106082616356001</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1106082616356001</v>
+        <v>8.262184722714837</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.262184722714837</v>
+        <v>1.806421150658787</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.806421150658787</v>
+        <v>10.17014190682963</v>
       </c>
       <c r="AB19" t="n">
-        <v>10.17014189771628</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0.006188448011409942</v>
-      </c>
-      <c r="AD19" t="inlineStr">
+        <v>0.006188447983211276</v>
+      </c>
+      <c r="AC19" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD19" t="n">
+        <v>2.517069101333618</v>
+      </c>
       <c r="AE19" t="n">
-        <v>1.026954889297485</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>6.623205184936523</v>
+        <v>6.560271263122559</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>698</v>
+      <c r="A20" t="n">
+        <v>18.05168677518481</v>
       </c>
       <c r="B20" t="n">
-        <v>18.05168677518481</v>
+        <v>21.54337168332784</v>
       </c>
       <c r="C20" t="n">
-        <v>21.54337168332784</v>
+        <v>40.14606294301679</v>
       </c>
       <c r="D20" t="n">
-        <v>40.14606294301679</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -2420,19 +2366,19 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>8.2606171846714</v>
       </c>
       <c r="M20" t="n">
-        <v>8.2606171846714</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>11.99826141379916</v>
       </c>
       <c r="P20" t="n">
-        <v>11.99826141379916</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -2441,62 +2387,59 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.01614337594564339</v>
       </c>
       <c r="T20" t="n">
-        <v>0.01614337594564339</v>
+        <v>1893.627935215775</v>
       </c>
       <c r="U20" t="n">
-        <v>1893.627935215775</v>
+        <v>200.3466927595986</v>
       </c>
       <c r="V20" t="n">
-        <v>200.3466927595986</v>
+        <v>-7.416595367999558</v>
       </c>
       <c r="W20" t="n">
-        <v>-7.416595367999558</v>
+        <v>3.504752859306902</v>
       </c>
       <c r="X20" t="n">
-        <v>3.504752859306902</v>
+        <v>0.1122998910665736</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.1122998910665736</v>
+        <v>8.143491897434147</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.143491897434147</v>
+        <v>1.835182866771414</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.835182866771414</v>
+        <v>10.26891571718882</v>
       </c>
       <c r="AB20" t="n">
-        <v>10.26891571494975</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0.005890243991493294</v>
-      </c>
-      <c r="AD20" t="inlineStr">
+        <v>0.005890243984899013</v>
+      </c>
+      <c r="AC20" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD20" t="n">
+        <v>2.523741483688354</v>
+      </c>
       <c r="AE20" t="n">
-        <v>1.120598793029785</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>7.009326457977295</v>
+        <v>6.812125205993652</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>699</v>
+      <c r="A21" t="n">
+        <v>17.30316829702608</v>
       </c>
       <c r="B21" t="n">
-        <v>17.30316829702608</v>
+        <v>20.30123682150807</v>
       </c>
       <c r="C21" t="n">
-        <v>20.30123682150807</v>
+        <v>35.00489144090659</v>
       </c>
       <c r="D21" t="n">
-        <v>35.00489144090659</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -2520,19 +2463,19 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>11.76946366999297</v>
       </c>
       <c r="M21" t="n">
-        <v>11.76946366999297</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>15.62123977056628</v>
       </c>
       <c r="P21" t="n">
-        <v>15.62123977056628</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -2541,62 +2484,59 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.01868295615421885</v>
       </c>
       <c r="T21" t="n">
-        <v>0.01868295615421885</v>
+        <v>1905.332029117198</v>
       </c>
       <c r="U21" t="n">
-        <v>1905.332029117198</v>
+        <v>202.8634158510409</v>
       </c>
       <c r="V21" t="n">
-        <v>202.8634158510409</v>
+        <v>-8.258354018609531</v>
       </c>
       <c r="W21" t="n">
-        <v>-8.258354018609531</v>
+        <v>3.932584226342296</v>
       </c>
       <c r="X21" t="n">
-        <v>3.932584226342296</v>
+        <v>0.1145360131513712</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1145360131513712</v>
+        <v>7.991016495067599</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.991016495067599</v>
+        <v>1.87334037985938</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.87334037985938</v>
+        <v>12.64495578003774</v>
       </c>
       <c r="AB21" t="n">
-        <v>12.64495577773897</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0.001795488967456071</v>
-      </c>
-      <c r="AD21" t="inlineStr">
+        <v>0.001795488965392278</v>
+      </c>
+      <c r="AC21" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD21" t="n">
+        <v>2.533707857131958</v>
+      </c>
       <c r="AE21" t="n">
-        <v>1.14710009098053</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>7.402275085449219</v>
+        <v>7.07982873916626</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>700</v>
+      <c r="A22" t="n">
+        <v>15.87142913305469</v>
       </c>
       <c r="B22" t="n">
-        <v>15.87142913305469</v>
+        <v>18.70576258983613</v>
       </c>
       <c r="C22" t="n">
-        <v>18.70576258983613</v>
+        <v>30.19464676324015</v>
       </c>
       <c r="D22" t="n">
-        <v>30.19464676324015</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -2620,19 +2560,19 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>16.67699386151701</v>
       </c>
       <c r="M22" t="n">
-        <v>16.67699386151701</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>18.55116765235202</v>
       </c>
       <c r="P22" t="n">
-        <v>18.55116765235202</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -2641,62 +2581,59 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.02132280954649748</v>
       </c>
       <c r="T22" t="n">
-        <v>0.02132280954649748</v>
+        <v>1921.130125222988</v>
       </c>
       <c r="U22" t="n">
-        <v>1921.130125222988</v>
+        <v>206.2241599538678</v>
       </c>
       <c r="V22" t="n">
-        <v>206.2241599538678</v>
+        <v>-9.369037117508064</v>
       </c>
       <c r="W22" t="n">
-        <v>-9.369037117508064</v>
+        <v>4.357480023472855</v>
       </c>
       <c r="X22" t="n">
-        <v>4.357480023472855</v>
+        <v>0.1175264069897883</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.1175264069897883</v>
+        <v>7.801207389430617</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.801207389430617</v>
+        <v>1.927101311134161</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.927101311134161</v>
+        <v>19.17827249355183</v>
       </c>
       <c r="AB22" t="n">
-        <v>19.17827249033544</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>6.846853610398274e-05</v>
-      </c>
-      <c r="AD22" t="inlineStr">
+        <v>6.846853599384861e-05</v>
+      </c>
+      <c r="AC22" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD22" t="n">
+        <v>2.604148149490356</v>
+      </c>
       <c r="AE22" t="n">
-        <v>1.148972630500793</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>7.839080333709717</v>
+        <v>7.500869750976562</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>701</v>
+      <c r="A23" t="n">
+        <v>16.2842163689804</v>
       </c>
       <c r="B23" t="n">
-        <v>16.2842163689804</v>
+        <v>11.62108928220617</v>
       </c>
       <c r="C23" t="n">
-        <v>11.62108928220617</v>
+        <v>69.68900737564974</v>
       </c>
       <c r="D23" t="n">
-        <v>69.68900737564974</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -2720,19 +2657,19 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.8209931388708622</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8209931388708622</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.584693834292852</v>
       </c>
       <c r="P23" t="n">
-        <v>1.584693834292852</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2741,62 +2678,59 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.005723659448972996</v>
       </c>
       <c r="T23" t="n">
-        <v>0.005723659448972996</v>
+        <v>1804.560680786897</v>
       </c>
       <c r="U23" t="n">
-        <v>1804.560680786897</v>
+        <v>152.9249193397706</v>
       </c>
       <c r="V23" t="n">
-        <v>152.9249193397706</v>
+        <v>-3.988340565739932</v>
       </c>
       <c r="W23" t="n">
-        <v>-3.988340565739932</v>
+        <v>1.698850637275885</v>
       </c>
       <c r="X23" t="n">
-        <v>1.698850637275885</v>
+        <v>0.08640015880863641</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.08640015880863641</v>
+        <v>9.092117900529091</v>
       </c>
       <c r="Z23" t="n">
-        <v>9.092117900529091</v>
+        <v>1.462526570850697</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.462526570850697</v>
+        <v>28.29366450194829</v>
       </c>
       <c r="AB23" t="n">
-        <v>28.29366448477043</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>7.17974170783009e-07</v>
-      </c>
-      <c r="AD23" t="inlineStr">
+        <v>7.1797416456576e-07</v>
+      </c>
+      <c r="AC23" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD23" t="n">
+        <v>0.9674618244171143</v>
+      </c>
       <c r="AE23" t="n">
-        <v>-0.1439922004938126</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>5.163097858428955</v>
+        <v>5.256033420562744</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>702</v>
+      <c r="A24" t="n">
+        <v>17.99859633271077</v>
       </c>
       <c r="B24" t="n">
-        <v>17.99859633271077</v>
+        <v>13.66150507969354</v>
       </c>
       <c r="C24" t="n">
-        <v>13.66150507969354</v>
+        <v>65.18010332095461</v>
       </c>
       <c r="D24" t="n">
-        <v>65.18010332095461</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -2820,19 +2754,19 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.177828825037154</v>
       </c>
       <c r="M24" t="n">
-        <v>1.177828825037154</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.981966441603931</v>
       </c>
       <c r="P24" t="n">
-        <v>1.981966441603931</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2841,62 +2775,59 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>0.006749019107849593</v>
       </c>
       <c r="T24" t="n">
-        <v>0.006749019107849593</v>
+        <v>1817.809745225328</v>
       </c>
       <c r="U24" t="n">
-        <v>1817.809745225328</v>
+        <v>163.0853992397982</v>
       </c>
       <c r="V24" t="n">
-        <v>163.0853992397982</v>
+        <v>-4.463667374112369</v>
       </c>
       <c r="W24" t="n">
-        <v>-4.463667374112369</v>
+        <v>1.875574231757871</v>
       </c>
       <c r="X24" t="n">
-        <v>1.875574231757871</v>
+        <v>0.09171317174128543</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.09171317174128543</v>
+        <v>8.947225319860511</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.947225319860511</v>
+        <v>1.541251999619234</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.541251999619234</v>
+        <v>21.00885113812373</v>
       </c>
       <c r="AB24" t="n">
-        <v>21.00885112085052</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.741485439061719e-05</v>
-      </c>
-      <c r="AD24" t="inlineStr">
+        <v>2.741485415380662e-05</v>
+      </c>
+      <c r="AC24" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD24" t="n">
+        <v>1.288498282432556</v>
+      </c>
       <c r="AE24" t="n">
-        <v>0.2256627380847931</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>5.159304141998291</v>
+        <v>5.321900367736816</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>703</v>
+      <c r="A25" t="n">
+        <v>19.53665474474453</v>
       </c>
       <c r="B25" t="n">
-        <v>19.53665474474453</v>
+        <v>15.08229893964224</v>
       </c>
       <c r="C25" t="n">
-        <v>15.08229893964224</v>
+        <v>60.56757689120469</v>
       </c>
       <c r="D25" t="n">
-        <v>60.56757689120469</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -2920,19 +2851,19 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.808989009252903</v>
       </c>
       <c r="M25" t="n">
-        <v>1.808989009252903</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.004480415155629</v>
       </c>
       <c r="P25" t="n">
-        <v>3.004480415155629</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2941,62 +2872,59 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>0.00821773094061517</v>
       </c>
       <c r="T25" t="n">
-        <v>0.00821773094061517</v>
+        <v>1829.427349919213</v>
       </c>
       <c r="U25" t="n">
-        <v>1829.427349919213</v>
+        <v>170.3345833808895</v>
       </c>
       <c r="V25" t="n">
-        <v>170.3345833808895</v>
+        <v>-4.901209198758062</v>
       </c>
       <c r="W25" t="n">
-        <v>-4.901209198758062</v>
+        <v>2.130049961671903</v>
       </c>
       <c r="X25" t="n">
-        <v>2.130049961671903</v>
+        <v>0.09559112743688601</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.09559112743688601</v>
+        <v>8.812242166582951</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.812242166582951</v>
+        <v>1.599506567855235</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.599506567855235</v>
+        <v>15.61003672203906</v>
       </c>
       <c r="AB25" t="n">
-        <v>15.61003670558257</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0.0004076839350397599</v>
-      </c>
-      <c r="AD25" t="inlineStr">
+        <v>0.000407683931685332</v>
+      </c>
+      <c r="AC25" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD25" t="n">
+        <v>1.548033237457275</v>
+      </c>
       <c r="AE25" t="n">
-        <v>0.3791229426860809</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>5.426104068756104</v>
+        <v>5.546070098876953</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>704</v>
+      <c r="A26" t="n">
+        <v>21.18080958029204</v>
       </c>
       <c r="B26" t="n">
-        <v>21.18080958029204</v>
+        <v>16.41888276730987</v>
       </c>
       <c r="C26" t="n">
-        <v>16.41888276730987</v>
+        <v>55.49755604733809</v>
       </c>
       <c r="D26" t="n">
-        <v>55.49755604733809</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -3020,19 +2948,19 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.78582109936913</v>
       </c>
       <c r="M26" t="n">
-        <v>2.78582109936913</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.116930505690866</v>
       </c>
       <c r="P26" t="n">
-        <v>4.116930505690866</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -3041,62 +2969,59 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>0.01002327231053391</v>
       </c>
       <c r="T26" t="n">
-        <v>0.01002327231053391</v>
+        <v>1842.372971012488</v>
       </c>
       <c r="U26" t="n">
-        <v>1842.372971012488</v>
+        <v>177.2699889808056</v>
       </c>
       <c r="V26" t="n">
-        <v>177.2699889808056</v>
+        <v>-5.399374730227284</v>
       </c>
       <c r="W26" t="n">
-        <v>-5.399374730227284</v>
+        <v>2.433698483509787</v>
       </c>
       <c r="X26" t="n">
-        <v>2.433698483509787</v>
+        <v>0.09934216885025565</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.09934216885025565</v>
+        <v>8.660208966637217</v>
       </c>
       <c r="Z26" t="n">
-        <v>8.660208966637217</v>
+        <v>1.655542093125456</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.655542093125456</v>
+        <v>11.37095423006791</v>
       </c>
       <c r="AB26" t="n">
-        <v>11.37095422249303</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0.003394913111943065</v>
-      </c>
-      <c r="AD26" t="inlineStr">
+        <v>0.003394913099085128</v>
+      </c>
+      <c r="AC26" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD26" t="n">
+        <v>1.698782324790955</v>
+      </c>
       <c r="AE26" t="n">
-        <v>0.6299235820770264</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>5.80295467376709</v>
+        <v>5.919199466705322</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>705</v>
+      <c r="A27" t="n">
+        <v>22.36133238808863</v>
       </c>
       <c r="B27" t="n">
-        <v>22.36133238808863</v>
+        <v>17.68792718760798</v>
       </c>
       <c r="C27" t="n">
-        <v>17.68792718760798</v>
+        <v>50.01949321582786</v>
       </c>
       <c r="D27" t="n">
-        <v>50.01949321582786</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -3120,19 +3045,19 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>4.251063367731021</v>
       </c>
       <c r="M27" t="n">
-        <v>4.251063367731021</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>5.680183840744505</v>
       </c>
       <c r="P27" t="n">
-        <v>5.680183840744505</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -3141,62 +3066,59 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>0.01215074305096257</v>
       </c>
       <c r="T27" t="n">
-        <v>0.01215074305096257</v>
+        <v>1857.083503674675</v>
       </c>
       <c r="U27" t="n">
-        <v>1857.083503674675</v>
+        <v>184.2095798401118</v>
       </c>
       <c r="V27" t="n">
-        <v>184.2095798401118</v>
+        <v>-5.984408774734399</v>
       </c>
       <c r="W27" t="n">
-        <v>-5.984408774734399</v>
+        <v>2.786560182923776</v>
       </c>
       <c r="X27" t="n">
-        <v>2.786560182923776</v>
+        <v>0.1031558043979282</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.1031558043979282</v>
+        <v>8.490860210984831</v>
       </c>
       <c r="Z27" t="n">
-        <v>8.490860210984831</v>
+        <v>1.711073414995902</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.711073414995902</v>
+        <v>8.677994927738725</v>
       </c>
       <c r="AB27" t="n">
-        <v>8.677994924381357</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0.01304960436944413</v>
-      </c>
-      <c r="AD27" t="inlineStr">
+        <v>0.01304960434753799</v>
+      </c>
+      <c r="AC27" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD27" t="n">
+        <v>1.907567024230957</v>
+      </c>
       <c r="AE27" t="n">
-        <v>0.7117559313774109</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>6.328783512115479</v>
+        <v>6.276787757873535</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>706</v>
+      <c r="A28" t="n">
+        <v>22.25528267810615</v>
       </c>
       <c r="B28" t="n">
-        <v>22.25528267810615</v>
+        <v>18.13124569257213</v>
       </c>
       <c r="C28" t="n">
-        <v>18.13124569257213</v>
+        <v>45.94547501288871</v>
       </c>
       <c r="D28" t="n">
-        <v>45.94547501288871</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -3220,19 +3142,19 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>6.108469737958585</v>
       </c>
       <c r="M28" t="n">
-        <v>6.108469737958585</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>7.55952687847443</v>
       </c>
       <c r="P28" t="n">
-        <v>7.55952687847443</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -3241,62 +3163,59 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>0.01427997797680656</v>
       </c>
       <c r="T28" t="n">
-        <v>0.01427997797680656</v>
+        <v>1868.804889673751</v>
       </c>
       <c r="U28" t="n">
-        <v>1868.804889673751</v>
+        <v>189.3599180710088</v>
       </c>
       <c r="V28" t="n">
-        <v>189.3599180710088</v>
+        <v>-6.611892994554888</v>
       </c>
       <c r="W28" t="n">
-        <v>-6.611892994554888</v>
+        <v>3.144570772142395</v>
       </c>
       <c r="X28" t="n">
-        <v>3.144570772142395</v>
+        <v>0.1062935803509471</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.1062935803509471</v>
+        <v>8.358085298794862</v>
       </c>
       <c r="Z28" t="n">
-        <v>8.358085298794862</v>
+        <v>1.75956979738066</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75956979738066</v>
+        <v>7.847035152122011</v>
       </c>
       <c r="AB28" t="n">
-        <v>7.847035146665502</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0.01977142484493244</v>
-      </c>
-      <c r="AD28" t="inlineStr">
+        <v>0.01977142479099092</v>
+      </c>
+      <c r="AC28" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD28" t="n">
+        <v>2.140591621398926</v>
+      </c>
       <c r="AE28" t="n">
-        <v>0.8350648880004883</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>6.727015972137451</v>
+        <v>6.603052616119385</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>707</v>
+      <c r="A29" t="n">
+        <v>22.11853696692908</v>
       </c>
       <c r="B29" t="n">
-        <v>22.11853696692908</v>
+        <v>17.71834953868881</v>
       </c>
       <c r="C29" t="n">
-        <v>17.71834953868881</v>
+        <v>41.15294747467846</v>
       </c>
       <c r="D29" t="n">
-        <v>41.15294747467846</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -3320,19 +3239,19 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>9.179356354015789</v>
       </c>
       <c r="M29" t="n">
-        <v>9.179356354015789</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>9.830809665687847</v>
       </c>
       <c r="P29" t="n">
-        <v>9.830809665687847</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -3341,62 +3260,59 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>0.01702922256247048</v>
       </c>
       <c r="T29" t="n">
-        <v>0.01702922256247048</v>
+        <v>1882.375210236956</v>
       </c>
       <c r="U29" t="n">
-        <v>1882.375210236956</v>
+        <v>194.2879178623252</v>
       </c>
       <c r="V29" t="n">
-        <v>194.2879178623252</v>
+        <v>-7.499450700016688</v>
       </c>
       <c r="W29" t="n">
-        <v>-7.499450700016688</v>
+        <v>3.600336999345563</v>
       </c>
       <c r="X29" t="n">
-        <v>3.600336999345563</v>
+        <v>0.1096762510355988</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.1096762510355988</v>
+        <v>8.194409991601907</v>
       </c>
       <c r="Z29" t="n">
-        <v>8.194409991601907</v>
+        <v>1.816323965305568</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.816323965305568</v>
+        <v>8.393309238028678</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.393309242282077</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0.01504582671174826</v>
-      </c>
-      <c r="AD29" t="inlineStr">
+        <v>0.01504582674374622</v>
+      </c>
+      <c r="AC29" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD29" t="n">
+        <v>2.213643074035645</v>
+      </c>
       <c r="AE29" t="n">
-        <v>0.9533175826072693</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>7.258996963500977</v>
+        <v>7.002973556518555</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>708</v>
+      <c r="A30" t="n">
+        <v>21.13587239531939</v>
       </c>
       <c r="B30" t="n">
-        <v>21.13587239531939</v>
+        <v>17.34750983028886</v>
       </c>
       <c r="C30" t="n">
-        <v>17.34750983028886</v>
+        <v>36.11077555188695</v>
       </c>
       <c r="D30" t="n">
-        <v>36.11077555188695</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -3420,19 +3336,19 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>13.24930686414909</v>
       </c>
       <c r="M30" t="n">
-        <v>13.24930686414909</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>12.15653535835572</v>
       </c>
       <c r="P30" t="n">
-        <v>12.15653535835572</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -3441,62 +3357,59 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>0.01975233339717399</v>
       </c>
       <c r="T30" t="n">
-        <v>0.01975233339717399</v>
+        <v>1900.159295131961</v>
       </c>
       <c r="U30" t="n">
-        <v>1900.159295131961</v>
+        <v>200.0440324943598</v>
       </c>
       <c r="V30" t="n">
-        <v>200.0440324943598</v>
+        <v>-8.548720746551373</v>
       </c>
       <c r="W30" t="n">
-        <v>-8.548720746551373</v>
+        <v>4.045895082346354</v>
       </c>
       <c r="X30" t="n">
-        <v>4.045895082346354</v>
+        <v>0.1136031273724941</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.1136031273724941</v>
+        <v>7.994008236918264</v>
       </c>
       <c r="Z30" t="n">
-        <v>7.994008236918264</v>
+        <v>1.880414202539238</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.880414202539238</v>
+        <v>11.95549152821672</v>
       </c>
       <c r="AB30" t="n">
-        <v>11.9554915275298</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0.002534533294137997</v>
-      </c>
-      <c r="AD30" t="inlineStr">
+        <v>0.002534533293267471</v>
+      </c>
+      <c r="AC30" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD30" t="n">
+        <v>2.476745367050171</v>
+      </c>
       <c r="AE30" t="n">
-        <v>1.117595434188843</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>7.747937202453613</v>
+        <v>7.40365743637085</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>709</v>
+      <c r="A31" t="n">
+        <v>19.80061812897557</v>
       </c>
       <c r="B31" t="n">
-        <v>19.80061812897557</v>
+        <v>15.3476838701526</v>
       </c>
       <c r="C31" t="n">
-        <v>15.3476838701526</v>
+        <v>31.05738066946694</v>
       </c>
       <c r="D31" t="n">
-        <v>31.05738066946694</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -3520,19 +3433,19 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>18.52044105582995</v>
       </c>
       <c r="M31" t="n">
-        <v>18.52044105582995</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>15.27387627557495</v>
       </c>
       <c r="P31" t="n">
-        <v>15.27387627557495</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -3541,62 +3454,59 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>0.02234030920231088</v>
       </c>
       <c r="T31" t="n">
-        <v>0.02234030920231088</v>
+        <v>1915.960217012119</v>
       </c>
       <c r="U31" t="n">
-        <v>1915.960217012119</v>
+        <v>203.730676930795</v>
       </c>
       <c r="V31" t="n">
-        <v>203.730676930795</v>
+        <v>-9.698632590650735</v>
       </c>
       <c r="W31" t="n">
-        <v>-9.698632590650735</v>
+        <v>4.468587469008692</v>
       </c>
       <c r="X31" t="n">
-        <v>4.468587469008692</v>
+        <v>0.1167826777879098</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.1167826777879098</v>
+        <v>7.798211181117483</v>
       </c>
       <c r="Z31" t="n">
-        <v>7.798211181117483</v>
+        <v>1.93635772262265</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.93635772262265</v>
+        <v>18.99365696264181</v>
       </c>
       <c r="AB31" t="n">
-        <v>18.99365695904121</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>7.508960084756655e-05</v>
-      </c>
-      <c r="AD31" t="inlineStr">
+        <v>7.508960071234139e-05</v>
+      </c>
+      <c r="AC31" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD31" t="n">
+        <v>2.56828761100769</v>
+      </c>
       <c r="AE31" t="n">
-        <v>1.027450203895569</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>8.083578109741211</v>
+        <v>7.703567504882812</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>710</v>
+      <c r="A32" t="n">
+        <v>20.55168297688286</v>
       </c>
       <c r="B32" t="n">
-        <v>20.55168297688286</v>
+        <v>8.905594154233439</v>
       </c>
       <c r="C32" t="n">
-        <v>8.905594154233439</v>
+        <v>68.38272010981913</v>
       </c>
       <c r="D32" t="n">
-        <v>68.38272010981913</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -3620,19 +3530,19 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>0.8751622996720143</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8751622996720143</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.284840459392553</v>
       </c>
       <c r="P32" t="n">
-        <v>1.284840459392553</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -3641,62 +3551,59 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>0.005939052764408702</v>
       </c>
       <c r="T32" t="n">
-        <v>0.005939052764408702</v>
+        <v>1794.910990541605</v>
       </c>
       <c r="U32" t="n">
-        <v>1794.910990541605</v>
+        <v>138.2348367575917</v>
       </c>
       <c r="V32" t="n">
-        <v>138.2348367575917</v>
+        <v>-3.627212047565354</v>
       </c>
       <c r="W32" t="n">
-        <v>-3.627212047565354</v>
+        <v>1.670883424475983</v>
       </c>
       <c r="X32" t="n">
-        <v>1.670883424475983</v>
+        <v>0.07929342216726326</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.07929342216726326</v>
+        <v>9.123059177693213</v>
       </c>
       <c r="Z32" t="n">
-        <v>9.123059177693213</v>
+        <v>1.380621884400646</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.380621884400646</v>
+        <v>26.92019417775388</v>
       </c>
       <c r="AB32" t="n">
-        <v>26.9201941662415</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.426770465995375e-06</v>
-      </c>
-      <c r="AD32" t="inlineStr">
+        <v>1.426770457779725e-06</v>
+      </c>
+      <c r="AC32" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD32" t="n">
+        <v>0.6263919472694397</v>
+      </c>
       <c r="AE32" t="n">
-        <v>-0.4066018462181091</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>5.341883182525635</v>
+        <v>5.399133682250977</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>711</v>
+      <c r="A33" t="n">
+        <v>22.96934284445093</v>
       </c>
       <c r="B33" t="n">
-        <v>22.96934284445093</v>
+        <v>10.46562148344112</v>
       </c>
       <c r="C33" t="n">
-        <v>10.46562148344112</v>
+        <v>63.38271594806355</v>
       </c>
       <c r="D33" t="n">
-        <v>63.38271594806355</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -3720,19 +3627,19 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.346310053130341</v>
       </c>
       <c r="M33" t="n">
-        <v>1.346310053130341</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.836009670914067</v>
       </c>
       <c r="P33" t="n">
-        <v>1.836009670914067</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3741,62 +3648,59 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>0.007232515461184539</v>
       </c>
       <c r="T33" t="n">
-        <v>0.007232515461184539</v>
+        <v>1807.075101769982</v>
       </c>
       <c r="U33" t="n">
-        <v>1807.075101769982</v>
+        <v>148.3855837262215</v>
       </c>
       <c r="V33" t="n">
-        <v>148.3855837262215</v>
+        <v>-4.104196058986292</v>
       </c>
       <c r="W33" t="n">
-        <v>-4.104196058986292</v>
+        <v>1.89372165719222</v>
       </c>
       <c r="X33" t="n">
-        <v>1.89372165719222</v>
+        <v>0.08458864201437863</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.08458864201437863</v>
+        <v>8.976601894533291</v>
       </c>
       <c r="Z33" t="n">
-        <v>8.976601894533291</v>
+        <v>1.458855759405878</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.458855759405878</v>
+        <v>19.08577388530037</v>
       </c>
       <c r="AB33" t="n">
-        <v>19.08577387566669</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>7.170952759305571e-05</v>
-      </c>
-      <c r="AD33" t="inlineStr">
+        <v>7.170952724766533e-05</v>
+      </c>
+      <c r="AC33" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD33" t="n">
+        <v>0.8965531587600708</v>
+      </c>
       <c r="AE33" t="n">
-        <v>-0.2240183353424072</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>5.325440406799316</v>
+        <v>5.454965591430664</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>712</v>
+      <c r="A34" t="n">
+        <v>24.40915250803127</v>
       </c>
       <c r="B34" t="n">
-        <v>24.40915250803127</v>
+        <v>11.68287684138104</v>
       </c>
       <c r="C34" t="n">
-        <v>11.68287684138104</v>
+        <v>59.44757449331301</v>
       </c>
       <c r="D34" t="n">
-        <v>59.44757449331301</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -3820,19 +3724,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.967267730406504</v>
       </c>
       <c r="M34" t="n">
-        <v>1.967267730406504</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.493128426868182</v>
       </c>
       <c r="P34" t="n">
-        <v>2.493128426868182</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -3841,62 +3745,59 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>0.008605828672474754</v>
       </c>
       <c r="T34" t="n">
-        <v>0.008605828672474754</v>
+        <v>1817.487709649119</v>
       </c>
       <c r="U34" t="n">
-        <v>1817.487709649119</v>
+        <v>156.3584478113895</v>
       </c>
       <c r="V34" t="n">
-        <v>156.3584478113895</v>
+        <v>-4.536849753213489</v>
       </c>
       <c r="W34" t="n">
-        <v>-4.536849753213489</v>
+        <v>2.128933800335837</v>
       </c>
       <c r="X34" t="n">
-        <v>2.128933800335837</v>
+        <v>0.08877970234386724</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.08877970234386724</v>
+        <v>8.856019026166464</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.856019026166464</v>
+        <v>1.519549263520379</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.519549263520379</v>
+        <v>14.46498169166072</v>
       </c>
       <c r="AB34" t="n">
-        <v>14.46498168750862</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0.0007227184405913523</v>
-      </c>
-      <c r="AD34" t="inlineStr">
+        <v>0.0007227184390909969</v>
+      </c>
+      <c r="AC34" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD34" t="n">
+        <v>1.045191645622253</v>
+      </c>
       <c r="AE34" t="n">
-        <v>0.01142206881195307</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>5.527170181274414</v>
+        <v>5.670511722564697</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>713</v>
+      <c r="A35" t="n">
+        <v>26.0811880993595</v>
       </c>
       <c r="B35" t="n">
-        <v>26.0811880993595</v>
+        <v>12.82909461563154</v>
       </c>
       <c r="C35" t="n">
-        <v>12.82909461563154</v>
+        <v>54.71950275831595</v>
       </c>
       <c r="D35" t="n">
-        <v>54.71950275831595</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3920,19 +3821,19 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.890844974398167</v>
       </c>
       <c r="M35" t="n">
-        <v>2.890844974398167</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.479369552294848</v>
       </c>
       <c r="P35" t="n">
-        <v>3.479369552294848</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -3941,62 +3842,59 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>0.01027318847935016</v>
       </c>
       <c r="T35" t="n">
-        <v>0.01027318847935016</v>
+        <v>1829.296006250463</v>
       </c>
       <c r="U35" t="n">
-        <v>1829.296006250463</v>
+        <v>164.0063235286174</v>
       </c>
       <c r="V35" t="n">
-        <v>164.0063235286174</v>
+        <v>-5.018933291525662</v>
       </c>
       <c r="W35" t="n">
-        <v>-5.018933291525662</v>
+        <v>2.407808995713729</v>
       </c>
       <c r="X35" t="n">
-        <v>2.407808995713729</v>
+        <v>0.09282595544178017</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.09282595544178017</v>
+        <v>8.715119611231668</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.715119611231668</v>
+        <v>1.577594998629744</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.577594998629744</v>
+        <v>10.52279221722411</v>
       </c>
       <c r="AB35" t="n">
-        <v>10.52279221183202</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0.005188056583811274</v>
-      </c>
-      <c r="AD35" t="inlineStr">
+        <v>0.005188056569824018</v>
+      </c>
+      <c r="AC35" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD35" t="n">
+        <v>1.272912740707397</v>
+      </c>
       <c r="AE35" t="n">
-        <v>0.1934209614992142</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>5.913045883178711</v>
+        <v>5.960551261901855</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>714</v>
+      <c r="A36" t="n">
+        <v>26.87614780904968</v>
       </c>
       <c r="B36" t="n">
-        <v>26.87614780904968</v>
+        <v>13.98389582130604</v>
       </c>
       <c r="C36" t="n">
-        <v>13.98389582130604</v>
+        <v>50.26300520655828</v>
       </c>
       <c r="D36" t="n">
-        <v>50.26300520655828</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -4020,19 +3918,19 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>4.299361166965641</v>
       </c>
       <c r="M36" t="n">
-        <v>4.299361166965641</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>4.577589996120354</v>
       </c>
       <c r="P36" t="n">
-        <v>4.577589996120354</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -4041,62 +3939,59 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>0.012304053703362</v>
       </c>
       <c r="T36" t="n">
-        <v>0.012304053703362</v>
+        <v>1842.784974665828</v>
       </c>
       <c r="U36" t="n">
-        <v>1842.784974665828</v>
+        <v>172.3796481356425</v>
       </c>
       <c r="V36" t="n">
-        <v>172.3796481356425</v>
+        <v>-5.638283745874877</v>
       </c>
       <c r="W36" t="n">
-        <v>-5.638283745874877</v>
+        <v>2.742104947225994</v>
       </c>
       <c r="X36" t="n">
-        <v>2.742104947225994</v>
+        <v>0.09737182311067256</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.09737182311067256</v>
+        <v>8.565031665175551</v>
       </c>
       <c r="Z36" t="n">
-        <v>8.565031665175551</v>
+        <v>1.642908185162571</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.642908185162571</v>
+        <v>8.120916674380208</v>
       </c>
       <c r="AB36" t="n">
-        <v>8.120916672585677</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0.01724111507536241</v>
-      </c>
-      <c r="AD36" t="inlineStr">
+        <v>0.01724111505989256</v>
+      </c>
+      <c r="AC36" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD36" t="n">
+        <v>1.515089273452759</v>
+      </c>
       <c r="AE36" t="n">
-        <v>0.3330166041851044</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>6.334460258483887</v>
+        <v>6.311192989349365</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>715</v>
+      <c r="A37" t="n">
+        <v>27.16629873490772</v>
       </c>
       <c r="B37" t="n">
-        <v>27.16629873490772</v>
+        <v>14.12400345615574</v>
       </c>
       <c r="C37" t="n">
-        <v>14.12400345615574</v>
+        <v>45.95401605145616</v>
       </c>
       <c r="D37" t="n">
-        <v>45.95401605145616</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -4120,19 +4015,19 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>6.394207957975715</v>
       </c>
       <c r="M37" t="n">
-        <v>6.394207957975715</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>6.361473799504655</v>
       </c>
       <c r="P37" t="n">
-        <v>6.361473799504655</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -4141,62 +4036,59 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>0.01469244808544889</v>
       </c>
       <c r="T37" t="n">
-        <v>0.01469244808544889</v>
+        <v>1854.561268107208</v>
       </c>
       <c r="U37" t="n">
-        <v>1854.561268107208</v>
+        <v>178.5666106502817</v>
       </c>
       <c r="V37" t="n">
-        <v>178.5666106502817</v>
+        <v>-6.359945988637914</v>
       </c>
       <c r="W37" t="n">
-        <v>-6.359945988637914</v>
+        <v>3.137295511079061</v>
       </c>
       <c r="X37" t="n">
-        <v>3.137295511079061</v>
+        <v>0.1011228801640802</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.1011228801640802</v>
+        <v>8.424918856387032</v>
       </c>
       <c r="Z37" t="n">
-        <v>8.424918856387032</v>
+        <v>1.701199642985428</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.701199642985428</v>
+        <v>6.931471962960424</v>
       </c>
       <c r="AB37" t="n">
-        <v>6.931471960897396</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0.03124999757346969</v>
-      </c>
-      <c r="AD37" t="inlineStr">
+        <v>0.03124999754123492</v>
+      </c>
+      <c r="AC37" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD37" t="n">
+        <v>1.7814701795578</v>
+      </c>
       <c r="AE37" t="n">
-        <v>0.5839120149612427</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>6.826303005218506</v>
+        <v>6.76977014541626</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>716</v>
+      <c r="A38" t="n">
+        <v>27.25598473560972</v>
       </c>
       <c r="B38" t="n">
-        <v>27.25598473560972</v>
+        <v>14.63372456545034</v>
       </c>
       <c r="C38" t="n">
-        <v>14.63372456545034</v>
+        <v>40.35557986617545</v>
       </c>
       <c r="D38" t="n">
-        <v>40.35557986617545</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -4220,19 +4112,19 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>9.346219422510915</v>
       </c>
       <c r="M38" t="n">
-        <v>9.346219422510915</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>8.408491410253575</v>
       </c>
       <c r="P38" t="n">
-        <v>8.408491410253575</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -4241,62 +4133,59 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>0.01729539590075853</v>
       </c>
       <c r="T38" t="n">
-        <v>0.01729539590075853</v>
+        <v>1872.067925524716</v>
       </c>
       <c r="U38" t="n">
-        <v>1872.067925524716</v>
+        <v>186.5540617936104</v>
       </c>
       <c r="V38" t="n">
-        <v>186.5540617936104</v>
+        <v>-7.246248283020125</v>
       </c>
       <c r="W38" t="n">
-        <v>-7.246248283020125</v>
+        <v>3.551442337604172</v>
       </c>
       <c r="X38" t="n">
-        <v>3.551442337604172</v>
+        <v>0.1057665398151225</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.1057665398151225</v>
+        <v>8.226857706546527</v>
       </c>
       <c r="Z38" t="n">
-        <v>8.226857706546527</v>
+        <v>1.76865331408857</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.76865331408857</v>
+        <v>7.501301992787466</v>
       </c>
       <c r="AB38" t="n">
-        <v>7.501301997375069</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.02350244081664388</v>
-      </c>
-      <c r="AD38" t="inlineStr">
+        <v>0.02350244087055375</v>
+      </c>
+      <c r="AC38" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD38" t="n">
+        <v>2.058291912078857</v>
+      </c>
       <c r="AE38" t="n">
-        <v>0.755460798740387</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>7.252737998962402</v>
+        <v>7.050463199615479</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>717</v>
+      <c r="A39" t="n">
+        <v>26.04628332899345</v>
       </c>
       <c r="B39" t="n">
-        <v>26.04628332899345</v>
+        <v>13.61795025241505</v>
       </c>
       <c r="C39" t="n">
-        <v>13.61795025241505</v>
+        <v>36.0083723955829</v>
       </c>
       <c r="D39" t="n">
-        <v>36.0083723955829</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -4320,19 +4209,19 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>14.07280166252771</v>
       </c>
       <c r="M39" t="n">
-        <v>14.07280166252771</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>10.25459236048089</v>
       </c>
       <c r="P39" t="n">
-        <v>10.25459236048089</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -4341,62 +4230,59 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>0.02040341691168338</v>
       </c>
       <c r="T39" t="n">
-        <v>0.02040341691168338</v>
+        <v>1889.682944261102</v>
       </c>
       <c r="U39" t="n">
-        <v>1889.682944261102</v>
+        <v>193.8519895500959</v>
       </c>
       <c r="V39" t="n">
-        <v>193.8519895500959</v>
+        <v>-8.535413313873866</v>
       </c>
       <c r="W39" t="n">
-        <v>-8.535413313873866</v>
+        <v>4.057449977785367</v>
       </c>
       <c r="X39" t="n">
-        <v>4.057449977785367</v>
+        <v>0.1107897469695056</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.1107897469695056</v>
+        <v>8.027035640431178</v>
       </c>
       <c r="Z39" t="n">
-        <v>8.027035640431178</v>
+        <v>1.854103709551148</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.854103709551148</v>
+        <v>11.26124461063933</v>
       </c>
       <c r="AB39" t="n">
-        <v>11.26124461576847</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0.00358634282333703</v>
-      </c>
-      <c r="AD39" t="inlineStr">
+        <v>0.00358634283253445</v>
+      </c>
+      <c r="AC39" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD39" t="n">
+        <v>2.362399339675903</v>
+      </c>
       <c r="AE39" t="n">
-        <v>1.111003279685974</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>7.880680561065674</v>
+        <v>7.462210655212402</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>718</v>
+      <c r="A40" t="n">
+        <v>23.96978635149335</v>
       </c>
       <c r="B40" t="n">
-        <v>23.96978635149335</v>
+        <v>13.40941150587545</v>
       </c>
       <c r="C40" t="n">
-        <v>13.40941150587545</v>
+        <v>31.11999433631694</v>
       </c>
       <c r="D40" t="n">
-        <v>31.11999433631694</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -4420,19 +4306,19 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>19.38461120783668</v>
       </c>
       <c r="M40" t="n">
-        <v>19.38461120783668</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>12.11619659847759</v>
       </c>
       <c r="P40" t="n">
-        <v>12.11619659847759</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -4441,62 +4327,59 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>0.0228740882022304</v>
       </c>
       <c r="T40" t="n">
-        <v>0.0228740882022304</v>
+        <v>1912.95414360032</v>
       </c>
       <c r="U40" t="n">
-        <v>1912.95414360032</v>
+        <v>201.2742052269745</v>
       </c>
       <c r="V40" t="n">
-        <v>201.2742052269745</v>
+        <v>-9.70337650788205</v>
       </c>
       <c r="W40" t="n">
-        <v>-9.70337650788205</v>
+        <v>4.432880616201109</v>
       </c>
       <c r="X40" t="n">
-        <v>4.432880616201109</v>
+        <v>0.1155367071833451</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.1155367071833451</v>
+        <v>7.783009715263461</v>
       </c>
       <c r="Z40" t="n">
-        <v>7.783009715263461</v>
+        <v>1.92714942623951</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.92714942623951</v>
+        <v>19.24217477019707</v>
       </c>
       <c r="AB40" t="n">
-        <v>19.24217476999975</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>6.631546798785415e-05</v>
-      </c>
-      <c r="AD40" t="inlineStr">
+        <v>6.631546798130383e-05</v>
+      </c>
+      <c r="AC40" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD40" t="n">
+        <v>2.48302960395813</v>
+      </c>
       <c r="AE40" t="n">
-        <v>1.132601380348206</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>8.154211044311523</v>
+        <v>7.761291027069092</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>719</v>
+      <c r="A41" t="n">
+        <v>25.6116837653232</v>
       </c>
       <c r="B41" t="n">
-        <v>25.6116837653232</v>
+        <v>6.891003169588367</v>
       </c>
       <c r="C41" t="n">
-        <v>6.891003169588367</v>
+        <v>65.5039258201722</v>
       </c>
       <c r="D41" t="n">
-        <v>65.5039258201722</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -4520,19 +4403,19 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>0.8732193156344137</v>
       </c>
       <c r="M41" t="n">
-        <v>0.8732193156344137</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1.120167929281824</v>
       </c>
       <c r="P41" t="n">
-        <v>1.120167929281824</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -4541,62 +4424,59 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>0.005985722554952947</v>
       </c>
       <c r="T41" t="n">
-        <v>0.005985722554952947</v>
+        <v>1789.105901200297</v>
       </c>
       <c r="U41" t="n">
-        <v>1789.105901200297</v>
+        <v>125.1504573882852</v>
       </c>
       <c r="V41" t="n">
-        <v>125.1504573882852</v>
+        <v>-3.352284094386424</v>
       </c>
       <c r="W41" t="n">
-        <v>-3.352284094386424</v>
+        <v>1.599777915149974</v>
       </c>
       <c r="X41" t="n">
-        <v>1.599777915149974</v>
+        <v>0.073180109810408</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.073180109810408</v>
+        <v>9.10971344775762</v>
       </c>
       <c r="Z41" t="n">
-        <v>9.10971344775762</v>
+        <v>1.316324609641298</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.316324609641298</v>
+        <v>24.29194518337585</v>
       </c>
       <c r="AB41" t="n">
-        <v>24.29194516911395</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>5.309714001255905e-06</v>
-      </c>
-      <c r="AD41" t="inlineStr">
+        <v>5.3097139633973e-06</v>
+      </c>
+      <c r="AC41" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD41" t="n">
+        <v>0.1118344664573669</v>
+      </c>
       <c r="AE41" t="n">
-        <v>-1.056822657585144</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>5.407161712646484</v>
+        <v>5.050472259521484</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>720</v>
+      <c r="A42" t="n">
+        <v>28.41067839248494</v>
       </c>
       <c r="B42" t="n">
-        <v>28.41067839248494</v>
+        <v>8.044857591939921</v>
       </c>
       <c r="C42" t="n">
-        <v>8.044857591939921</v>
+        <v>60.64305460692668</v>
       </c>
       <c r="D42" t="n">
-        <v>60.64305460692668</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -4620,19 +4500,19 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.27353852194787</v>
       </c>
       <c r="M42" t="n">
-        <v>1.27353852194787</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1.627870886700589</v>
       </c>
       <c r="P42" t="n">
-        <v>1.627870886700589</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -4641,62 +4521,59 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>0.007110329218215425</v>
       </c>
       <c r="T42" t="n">
-        <v>0.007110329218215425</v>
+        <v>1799.250473681775</v>
       </c>
       <c r="U42" t="n">
-        <v>1799.250473681775</v>
+        <v>134.0924614145673</v>
       </c>
       <c r="V42" t="n">
-        <v>134.0924614145673</v>
+        <v>-3.727425762119625</v>
       </c>
       <c r="W42" t="n">
-        <v>-3.727425762119625</v>
+        <v>1.79411551312567</v>
       </c>
       <c r="X42" t="n">
-        <v>1.79411551312567</v>
+        <v>0.07770798014440843</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.07770798014440843</v>
+        <v>8.977317779911283</v>
       </c>
       <c r="Z42" t="n">
-        <v>8.977317779911283</v>
+        <v>1.380448262440932</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.380448262440932</v>
+        <v>17.83713282889721</v>
       </c>
       <c r="AB42" t="n">
-        <v>17.83713282533933</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0.0001338800360072279</v>
-      </c>
-      <c r="AD42" t="inlineStr">
+        <v>0.000133880035769085</v>
+      </c>
+      <c r="AC42" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD42" t="n">
+        <v>0.4365909099578857</v>
+      </c>
       <c r="AE42" t="n">
-        <v>-0.5473269820213318</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>5.575394153594971</v>
+        <v>5.624183177947998</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>721</v>
+      <c r="A43" t="n">
+        <v>30.68040031937237</v>
       </c>
       <c r="B43" t="n">
-        <v>30.68040031937237</v>
+        <v>8.898314990229773</v>
       </c>
       <c r="C43" t="n">
-        <v>8.898314990229773</v>
+        <v>56.45497452822937</v>
       </c>
       <c r="D43" t="n">
-        <v>56.45497452822937</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -4720,19 +4597,19 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.949218890633843</v>
       </c>
       <c r="M43" t="n">
-        <v>1.949218890633843</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.017091271534639</v>
       </c>
       <c r="P43" t="n">
-        <v>2.017091271534639</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -4741,62 +4618,59 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>0.00863808033441326</v>
       </c>
       <c r="T43" t="n">
-        <v>0.00863808033441326</v>
+        <v>1808.76384067771</v>
       </c>
       <c r="U43" t="n">
-        <v>1808.76384067771</v>
+        <v>141.7838651296247</v>
       </c>
       <c r="V43" t="n">
-        <v>141.7838651296247</v>
+        <v>-4.138784153391218</v>
       </c>
       <c r="W43" t="n">
-        <v>-4.138784153391218</v>
+        <v>2.041999223562375</v>
       </c>
       <c r="X43" t="n">
-        <v>2.041999223562375</v>
+        <v>0.08171077151635865</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.08171077151635865</v>
+        <v>8.855275619814973</v>
       </c>
       <c r="Z43" t="n">
-        <v>8.855275619814973</v>
+        <v>1.437625352181259</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.437625352181259</v>
+        <v>13.8301214939273</v>
       </c>
       <c r="AB43" t="n">
-        <v>13.83012149480425</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0.0009927211516509438</v>
-      </c>
-      <c r="AD43" t="inlineStr">
+        <v>0.0009927211520862622</v>
+      </c>
+      <c r="AC43" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD43" t="n">
+        <v>0.7252458930015564</v>
+      </c>
       <c r="AE43" t="n">
-        <v>-0.2788173854351044</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>5.845067977905273</v>
+        <v>5.860948085784912</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>722</v>
+      <c r="A44" t="n">
+        <v>32.34762367758118</v>
       </c>
       <c r="B44" t="n">
-        <v>32.34762367758118</v>
+        <v>9.978366632442803</v>
       </c>
       <c r="C44" t="n">
-        <v>9.978366632442803</v>
+        <v>52.0813212558916</v>
       </c>
       <c r="D44" t="n">
-        <v>52.0813212558916</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -4820,19 +4694,19 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.843106837929702</v>
       </c>
       <c r="M44" t="n">
-        <v>2.843106837929702</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.749581596154719</v>
       </c>
       <c r="P44" t="n">
-        <v>2.749581596154719</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -4841,62 +4715,59 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>0.01027236935138879</v>
       </c>
       <c r="T44" t="n">
-        <v>0.01027236935138879</v>
+        <v>1820.039738440432</v>
       </c>
       <c r="U44" t="n">
-        <v>1820.039738440432</v>
+        <v>150.5424983548378</v>
       </c>
       <c r="V44" t="n">
-        <v>150.5424983548378</v>
+        <v>-4.604448383643675</v>
       </c>
       <c r="W44" t="n">
-        <v>-4.604448383643675</v>
+        <v>2.307721894239452</v>
       </c>
       <c r="X44" t="n">
-        <v>2.307721894239452</v>
+        <v>0.08618063524205122</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.08618063524205122</v>
+        <v>8.721260727460336</v>
       </c>
       <c r="Z44" t="n">
-        <v>8.721260727460336</v>
+        <v>1.497675826014134</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.497675826014134</v>
+        <v>10.82153044907386</v>
       </c>
       <c r="AB44" t="n">
-        <v>10.82153045391246</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0.004468219700620502</v>
-      </c>
-      <c r="AD44" t="inlineStr">
+        <v>0.00446821971143041</v>
+      </c>
+      <c r="AC44" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD44" t="n">
+        <v>0.954977810382843</v>
+      </c>
       <c r="AE44" t="n">
-        <v>-0.1094250231981277</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>6.182117462158203</v>
+        <v>6.174372673034668</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>723</v>
+      <c r="A45" t="n">
+        <v>33.26712421235609</v>
       </c>
       <c r="B45" t="n">
-        <v>33.26712421235609</v>
+        <v>10.66178261003462</v>
       </c>
       <c r="C45" t="n">
-        <v>10.66178261003462</v>
+        <v>48.0364962515561</v>
       </c>
       <c r="D45" t="n">
-        <v>48.0364962515561</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -4920,19 +4791,19 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>4.232243536462632</v>
       </c>
       <c r="M45" t="n">
-        <v>4.232243536462632</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.802353389590545</v>
       </c>
       <c r="P45" t="n">
-        <v>3.802353389590545</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -4941,62 +4812,59 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>0.01231428695863964</v>
       </c>
       <c r="T45" t="n">
-        <v>0.01231428695863964</v>
+        <v>1831.299239219373</v>
       </c>
       <c r="U45" t="n">
-        <v>1831.299239219373</v>
+        <v>158.6078760156398</v>
       </c>
       <c r="V45" t="n">
-        <v>158.6078760156398</v>
+        <v>-5.180514748106642</v>
       </c>
       <c r="W45" t="n">
-        <v>-5.180514748106642</v>
+        <v>2.633986523217033</v>
       </c>
       <c r="X45" t="n">
-        <v>2.633986523217033</v>
+        <v>0.09053128741869934</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.09053128741869934</v>
+        <v>8.589800428198293</v>
       </c>
       <c r="Z45" t="n">
-        <v>8.589800428198293</v>
+        <v>1.558533015770604</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.558533015770604</v>
+        <v>8.955350253824074</v>
       </c>
       <c r="AB45" t="n">
-        <v>8.95535025952621</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0.01135979252201436</v>
-      </c>
-      <c r="AD45" t="inlineStr">
+        <v>0.01135979255440189</v>
+      </c>
+      <c r="AC45" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD45" t="n">
+        <v>1.177207231521606</v>
+      </c>
       <c r="AE45" t="n">
-        <v>0.1135851666331291</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>6.584229469299316</v>
+        <v>6.484439373016357</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>724</v>
+      <c r="A46" t="n">
+        <v>33.39925272231932</v>
       </c>
       <c r="B46" t="n">
-        <v>33.39925272231932</v>
+        <v>11.35006727185082</v>
       </c>
       <c r="C46" t="n">
-        <v>11.35006727185082</v>
+        <v>43.85245562775339</v>
       </c>
       <c r="D46" t="n">
-        <v>43.85245562775339</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -5020,19 +4888,19 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>6.545349612862421</v>
       </c>
       <c r="M46" t="n">
-        <v>6.545349612862421</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>4.85287476521403</v>
       </c>
       <c r="P46" t="n">
-        <v>4.85287476521403</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -5041,62 +4909,59 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>0.01495916889405634</v>
       </c>
       <c r="T46" t="n">
-        <v>0.01495916889405634</v>
+        <v>1846.388177677795</v>
       </c>
       <c r="U46" t="n">
-        <v>1846.388177677795</v>
+        <v>168.8383196541722</v>
       </c>
       <c r="V46" t="n">
-        <v>168.8383196541722</v>
+        <v>-6.044121021597624</v>
       </c>
       <c r="W46" t="n">
-        <v>-6.044121021597624</v>
+        <v>3.049405535777334</v>
       </c>
       <c r="X46" t="n">
-        <v>3.049405535777334</v>
+        <v>0.09624216603254504</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.09624216603254504</v>
+        <v>8.425291436723283</v>
       </c>
       <c r="Z46" t="n">
-        <v>8.425291436723283</v>
+        <v>1.641249905139774</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.641249905139774</v>
+        <v>8.02406880605724</v>
       </c>
       <c r="AB46" t="n">
-        <v>8.02406881722208</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0.01809654200136446</v>
-      </c>
-      <c r="AD46" t="inlineStr">
+        <v>0.01809654210238687</v>
+      </c>
+      <c r="AC46" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD46" t="n">
+        <v>1.531490206718445</v>
+      </c>
       <c r="AE46" t="n">
-        <v>0.4040507078170776</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>7.057461738586426</v>
+        <v>6.841854095458984</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>725</v>
+      <c r="A47" t="n">
+        <v>32.83385481517335</v>
       </c>
       <c r="B47" t="n">
-        <v>32.83385481517335</v>
+        <v>11.48725055530047</v>
       </c>
       <c r="C47" t="n">
-        <v>11.48725055530047</v>
+        <v>39.84170193873135</v>
       </c>
       <c r="D47" t="n">
-        <v>39.84170193873135</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -5120,19 +4985,19 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>9.348298941709157</v>
       </c>
       <c r="M47" t="n">
-        <v>9.348298941709157</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>6.488893749085666</v>
       </c>
       <c r="P47" t="n">
-        <v>6.488893749085666</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -5141,62 +5006,59 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>0.01743629115340805</v>
       </c>
       <c r="T47" t="n">
-        <v>0.01743629115340805</v>
+        <v>1860.800965761505</v>
       </c>
       <c r="U47" t="n">
-        <v>1860.800965761505</v>
+        <v>177.2088662756244</v>
       </c>
       <c r="V47" t="n">
-        <v>177.2088662756244</v>
+        <v>-6.935138924654915</v>
       </c>
       <c r="W47" t="n">
-        <v>-6.935138924654915</v>
+        <v>3.443682539669018</v>
       </c>
       <c r="X47" t="n">
-        <v>3.443682539669018</v>
+        <v>0.1011569661869414</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.1011569661869414</v>
+        <v>8.266860634374265</v>
       </c>
       <c r="Z47" t="n">
-        <v>8.266860634374265</v>
+        <v>1.714113191631074</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.714113191631074</v>
+        <v>8.405405773736398</v>
       </c>
       <c r="AB47" t="n">
-        <v>8.405405778971073</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0.0149551001601721</v>
-      </c>
-      <c r="AD47" t="inlineStr">
+        <v>0.01495510019931467</v>
+      </c>
+      <c r="AC47" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD47" t="n">
+        <v>1.835706353187561</v>
+      </c>
       <c r="AE47" t="n">
-        <v>0.6285002827644348</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>7.363792419433594</v>
+        <v>7.124486923217773</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>726</v>
+      <c r="A48" t="n">
+        <v>31.22587875804939</v>
       </c>
       <c r="B48" t="n">
-        <v>31.22587875804939</v>
+        <v>11.3685841516441</v>
       </c>
       <c r="C48" t="n">
-        <v>11.3685841516441</v>
+        <v>34.92232354679246</v>
       </c>
       <c r="D48" t="n">
-        <v>34.92232354679246</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -5220,19 +5082,19 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>14.42462712929108</v>
       </c>
       <c r="M48" t="n">
-        <v>14.42462712929108</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>8.058586414222969</v>
       </c>
       <c r="P48" t="n">
-        <v>8.058586414222969</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -5241,62 +5103,59 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>0.02075494273154538</v>
       </c>
       <c r="T48" t="n">
-        <v>0.02075494273154538</v>
+        <v>1883.934472518733</v>
       </c>
       <c r="U48" t="n">
-        <v>1883.934472518733</v>
+        <v>188.6070784106394</v>
       </c>
       <c r="V48" t="n">
-        <v>188.6070784106394</v>
+        <v>-8.340592916218087</v>
       </c>
       <c r="W48" t="n">
-        <v>-8.340592916218087</v>
+        <v>3.955150496361188</v>
       </c>
       <c r="X48" t="n">
-        <v>3.955150496361188</v>
+        <v>0.1080532242687294</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.1080532242687294</v>
+        <v>8.022301996617198</v>
       </c>
       <c r="Z48" t="n">
-        <v>8.022301996617198</v>
+        <v>1.820110306355468</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.820110306355468</v>
+        <v>12.33633313141917</v>
       </c>
       <c r="AB48" t="n">
-        <v>12.33633314300654</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0.002095073649143964</v>
-      </c>
-      <c r="AD48" t="inlineStr">
+        <v>0.002095073661282254</v>
+      </c>
+      <c r="AC48" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD48" t="n">
+        <v>2.209506511688232</v>
+      </c>
       <c r="AE48" t="n">
-        <v>1.007051110267639</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>7.978857040405273</v>
+        <v>7.58892297744751</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>727</v>
+      <c r="A49" t="n">
+        <v>28.00050845971687</v>
       </c>
       <c r="B49" t="n">
-        <v>28.00050845971687</v>
+        <v>11.25353181117791</v>
       </c>
       <c r="C49" t="n">
-        <v>11.25353181117791</v>
+        <v>31.12242471676077</v>
       </c>
       <c r="D49" t="n">
-        <v>31.12242471676077</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -5320,19 +5179,19 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>20.12114404994593</v>
       </c>
       <c r="M49" t="n">
-        <v>20.12114404994593</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>9.502390962398529</v>
       </c>
       <c r="P49" t="n">
-        <v>9.502390962398529</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -5341,62 +5200,59 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>0.02333668515548367</v>
       </c>
       <c r="T49" t="n">
-        <v>0.02333668515548367</v>
+        <v>1908.461926194631</v>
       </c>
       <c r="U49" t="n">
-        <v>1908.461926194631</v>
+        <v>198.2863400414355</v>
       </c>
       <c r="V49" t="n">
-        <v>198.2863400414355</v>
+        <v>-9.685545383428858</v>
       </c>
       <c r="W49" t="n">
-        <v>-9.685545383428858</v>
+        <v>4.367806736618214</v>
       </c>
       <c r="X49" t="n">
-        <v>4.367806736618214</v>
+        <v>0.1140930570564763</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.1140930570564763</v>
+        <v>7.780497813745046</v>
       </c>
       <c r="Z49" t="n">
-        <v>7.780497813745046</v>
+        <v>1.914868691477184</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.914868691477184</v>
+        <v>20.21279032124075</v>
       </c>
       <c r="AB49" t="n">
-        <v>20.21279032763764</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>4.081768299046828e-05</v>
-      </c>
-      <c r="AD49" t="inlineStr">
+        <v>4.081768312103051e-05</v>
+      </c>
+      <c r="AC49" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD49" t="n">
+        <v>2.431853532791138</v>
+      </c>
       <c r="AE49" t="n">
-        <v>1.033382534980774</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>8.121416091918945</v>
+        <v>7.724350452423096</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>728</v>
+      <c r="A50" t="n">
+        <v>32.75859992753161</v>
       </c>
       <c r="B50" t="n">
-        <v>32.75859992753161</v>
+        <v>5.573665496030907</v>
       </c>
       <c r="C50" t="n">
-        <v>5.573665496030907</v>
+        <v>59.73922474830303</v>
       </c>
       <c r="D50" t="n">
-        <v>59.73922474830303</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -5420,19 +5276,19 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>0.8893515950869282</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8893515950869282</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1.039158233047526</v>
       </c>
       <c r="P50" t="n">
-        <v>1.039158233047526</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -5441,62 +5297,59 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>0.006095786288845258</v>
       </c>
       <c r="T50" t="n">
-        <v>0.006095786288845258</v>
+        <v>1788.564284731499</v>
       </c>
       <c r="U50" t="n">
-        <v>1788.564284731499</v>
+        <v>115.1903414599131</v>
       </c>
       <c r="V50" t="n">
-        <v>115.1903414599131</v>
+        <v>-3.196618219872452</v>
       </c>
       <c r="W50" t="n">
-        <v>-3.196618219872452</v>
+        <v>1.520305149933684</v>
       </c>
       <c r="X50" t="n">
-        <v>1.520305149933684</v>
+        <v>0.06873545438315187</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.06873545438315187</v>
+        <v>9.022792524285752</v>
       </c>
       <c r="Z50" t="n">
-        <v>9.022792524285752</v>
+        <v>1.276817161411238</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.276817161411238</v>
+        <v>20.40224680011904</v>
       </c>
       <c r="AB50" t="n">
-        <v>20.4022467986937</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>3.712858501858651e-05</v>
-      </c>
-      <c r="AD50" t="inlineStr">
+        <v>3.71285849921632e-05</v>
+      </c>
+      <c r="AC50" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD50" t="n">
+        <v>0.2687427699565887</v>
+      </c>
       <c r="AE50" t="n">
-        <v>-0.5742098093032837</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>5.748656749725342</v>
+        <v>5.802199363708496</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>729</v>
+      <c r="A51" t="n">
+        <v>35.60454595063857</v>
       </c>
       <c r="B51" t="n">
-        <v>35.60454595063857</v>
+        <v>6.384230536662519</v>
       </c>
       <c r="C51" t="n">
-        <v>6.384230536662519</v>
+        <v>55.41123198552285</v>
       </c>
       <c r="D51" t="n">
-        <v>55.41123198552285</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -5520,19 +5373,19 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.258086825061164</v>
       </c>
       <c r="M51" t="n">
-        <v>1.258086825061164</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>1.341904702114899</v>
       </c>
       <c r="P51" t="n">
-        <v>1.341904702114899</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -5541,62 +5394,59 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>0.007128359451633718</v>
       </c>
       <c r="T51" t="n">
-        <v>0.007128359451633718</v>
+        <v>1796.818681683573</v>
       </c>
       <c r="U51" t="n">
-        <v>1796.818681683573</v>
+        <v>122.5933166383642</v>
       </c>
       <c r="V51" t="n">
-        <v>122.5933166383642</v>
+        <v>-3.470766706101379</v>
       </c>
       <c r="W51" t="n">
-        <v>-3.470766706101379</v>
+        <v>1.68934706564176</v>
       </c>
       <c r="X51" t="n">
-        <v>1.68934706564176</v>
+        <v>0.0723061979511995</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.0723061979511995</v>
+        <v>8.908322494404782</v>
       </c>
       <c r="Z51" t="n">
-        <v>8.908322494404782</v>
+        <v>1.323155177163384</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.323155177163384</v>
+        <v>16.9580189016226</v>
       </c>
       <c r="AB51" t="n">
-        <v>16.95801892064027</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0.0002077844195279566</v>
-      </c>
-      <c r="AD51" t="inlineStr">
+        <v>0.0002077844215037095</v>
+      </c>
+      <c r="AC51" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD51" t="n">
+        <v>0.4349464476108551</v>
+      </c>
       <c r="AE51" t="n">
-        <v>-0.4520371854305267</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>5.965620040893555</v>
+        <v>6.008243560791016</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>730</v>
+      <c r="A52" t="n">
+        <v>38.13811789539464</v>
       </c>
       <c r="B52" t="n">
-        <v>38.13811789539464</v>
+        <v>6.901093732753926</v>
       </c>
       <c r="C52" t="n">
-        <v>6.901093732753926</v>
+        <v>51.41799930683538</v>
       </c>
       <c r="D52" t="n">
-        <v>51.41799930683538</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -5620,19 +5470,19 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.752883934036925</v>
       </c>
       <c r="M52" t="n">
-        <v>1.752883934036925</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1.78990513097912</v>
       </c>
       <c r="P52" t="n">
-        <v>1.78990513097912</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -5641,62 +5491,59 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>0.008294079547027725</v>
       </c>
       <c r="T52" t="n">
-        <v>0.008294079547027725</v>
+        <v>1804.029908247308</v>
       </c>
       <c r="U52" t="n">
-        <v>1804.029908247308</v>
+        <v>128.1360299999582</v>
       </c>
       <c r="V52" t="n">
-        <v>128.1360299999582</v>
+        <v>-3.719434506810907</v>
       </c>
       <c r="W52" t="n">
-        <v>-3.719434506810907</v>
+        <v>1.86547272251768</v>
       </c>
       <c r="X52" t="n">
-        <v>1.86547272251768</v>
+        <v>0.07501018829817835</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.07501018829817835</v>
+        <v>8.804901937406056</v>
       </c>
       <c r="Z52" t="n">
-        <v>8.804901937406056</v>
+        <v>1.357568245523672</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.357568245523672</v>
+        <v>15.22731190730093</v>
       </c>
       <c r="AB52" t="n">
-        <v>15.22731192184075</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0.0004936637399449717</v>
-      </c>
-      <c r="AD52" t="inlineStr">
+        <v>0.0004936637435338787</v>
+      </c>
+      <c r="AC52" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD52" t="n">
+        <v>0.4766562283039093</v>
+      </c>
       <c r="AE52" t="n">
-        <v>-0.4213981032371521</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>6.067948818206787</v>
+        <v>6.16117000579834</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>731</v>
+      <c r="A53" t="n">
+        <v>39.1380055059179</v>
       </c>
       <c r="B53" t="n">
-        <v>39.1380055059179</v>
+        <v>7.636039101874935</v>
       </c>
       <c r="C53" t="n">
-        <v>7.636039101874935</v>
+        <v>48.26557354651341</v>
       </c>
       <c r="D53" t="n">
-        <v>48.26557354651341</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -5720,19 +5567,19 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.646214637996664</v>
       </c>
       <c r="M53" t="n">
-        <v>2.646214637996664</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.314167207697084</v>
       </c>
       <c r="P53" t="n">
-        <v>2.314167207697084</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -5741,62 +5588,59 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>0.01000720715854496</v>
       </c>
       <c r="T53" t="n">
-        <v>0.01000720715854496</v>
+        <v>1813.027975527215</v>
       </c>
       <c r="U53" t="n">
-        <v>1813.027975527215</v>
+        <v>136.7064244342563</v>
       </c>
       <c r="V53" t="n">
-        <v>136.7064244342563</v>
+        <v>-4.151003253594608</v>
       </c>
       <c r="W53" t="n">
-        <v>-4.151003253594608</v>
+        <v>2.141067640128211</v>
       </c>
       <c r="X53" t="n">
-        <v>2.141067640128211</v>
+        <v>0.07934200511986528</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.07934200511986528</v>
+        <v>8.700864600145554</v>
       </c>
       <c r="Z53" t="n">
-        <v>8.700864600145554</v>
+        <v>1.413398103016241</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.413398103016241</v>
+        <v>13.56531395559864</v>
       </c>
       <c r="AB53" t="n">
-        <v>13.56531396418105</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0.001133259843512091</v>
-      </c>
-      <c r="AD53" t="inlineStr">
+        <v>0.00113325984837509</v>
+      </c>
+      <c r="AC53" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD53" t="n">
+        <v>0.748300313949585</v>
+      </c>
       <c r="AE53" t="n">
-        <v>-0.3318018615245819</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>6.435742855072021</v>
+        <v>6.305307865142822</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>732</v>
+      <c r="A54" t="n">
+        <v>40.17007780104868</v>
       </c>
       <c r="B54" t="n">
-        <v>40.17007780104868</v>
+        <v>8.270604400236421</v>
       </c>
       <c r="C54" t="n">
-        <v>8.270604400236421</v>
+        <v>44.39734559290023</v>
       </c>
       <c r="D54" t="n">
-        <v>44.39734559290023</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -5820,19 +5664,19 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>4.141460551104069</v>
       </c>
       <c r="M54" t="n">
-        <v>4.141460551104069</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.020511654710611</v>
       </c>
       <c r="P54" t="n">
-        <v>3.020511654710611</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -5841,62 +5685,59 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>0.01227551845386234</v>
       </c>
       <c r="T54" t="n">
-        <v>0.01227551845386234</v>
+        <v>1824.550618061278</v>
       </c>
       <c r="U54" t="n">
-        <v>1824.550618061278</v>
+        <v>146.4191650147858</v>
       </c>
       <c r="V54" t="n">
-        <v>146.4191650147858</v>
+        <v>-4.757179788436318</v>
       </c>
       <c r="W54" t="n">
-        <v>-4.757179788436318</v>
+        <v>2.485238178044922</v>
       </c>
       <c r="X54" t="n">
-        <v>2.485238178044922</v>
+        <v>0.08442431196365888</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.08442431196365888</v>
+        <v>8.567005346020188</v>
       </c>
       <c r="Z54" t="n">
-        <v>8.567005346020188</v>
+        <v>1.481049154564836</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.481049154564836</v>
+        <v>12.43430185197348</v>
       </c>
       <c r="AB54" t="n">
-        <v>12.43430186738783</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0.001994920789990529</v>
-      </c>
-      <c r="AD54" t="inlineStr">
+        <v>0.001994920805365785</v>
+      </c>
+      <c r="AC54" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD54" t="n">
+        <v>0.9953310489654541</v>
+      </c>
       <c r="AE54" t="n">
-        <v>-0.1088833138346672</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>6.76712703704834</v>
+        <v>6.580316543579102</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>733</v>
+      <c r="A55" t="n">
+        <v>40.31777520333784</v>
       </c>
       <c r="B55" t="n">
-        <v>40.31777520333784</v>
+        <v>8.64227767036617</v>
       </c>
       <c r="C55" t="n">
-        <v>8.64227767036617</v>
+        <v>40.91661268027966</v>
       </c>
       <c r="D55" t="n">
-        <v>40.91661268027966</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -5920,19 +5761,19 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>6.171777873210093</v>
       </c>
       <c r="M55" t="n">
-        <v>6.171777873210093</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.951556572806229</v>
       </c>
       <c r="P55" t="n">
-        <v>3.951556572806229</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -5941,62 +5782,59 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>0.01468111055202743</v>
       </c>
       <c r="T55" t="n">
-        <v>0.01468111055202743</v>
+        <v>1836.743187122582</v>
       </c>
       <c r="U55" t="n">
-        <v>1836.743187122582</v>
+        <v>155.9787304874811</v>
       </c>
       <c r="V55" t="n">
-        <v>155.9787304874811</v>
+        <v>-5.49034804907873</v>
       </c>
       <c r="W55" t="n">
-        <v>-5.49034804907873</v>
+        <v>2.845935735902519</v>
       </c>
       <c r="X55" t="n">
-        <v>2.845935735902519</v>
+        <v>0.08965051680342165</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.08965051680342165</v>
+        <v>8.431592381459648</v>
       </c>
       <c r="Z55" t="n">
-        <v>8.431592381459648</v>
+        <v>1.553559684143321</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.553559684143321</v>
+        <v>11.82356034151155</v>
       </c>
       <c r="AB55" t="n">
-        <v>11.82356035173796</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0.00270736301268415</v>
-      </c>
-      <c r="AD55" t="inlineStr">
+        <v>0.00270736302652741</v>
+      </c>
+      <c r="AC55" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD55" t="n">
+        <v>1.270704388618469</v>
+      </c>
       <c r="AE55" t="n">
-        <v>0.1014297679066658</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>7.04632043838501</v>
+        <v>6.907936573028564</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>734</v>
+      <c r="A56" t="n">
+        <v>38.89328689858721</v>
       </c>
       <c r="B56" t="n">
-        <v>38.89328689858721</v>
+        <v>9.076333403675443</v>
       </c>
       <c r="C56" t="n">
-        <v>9.076333403675443</v>
+        <v>37.8452547701464</v>
       </c>
       <c r="D56" t="n">
-        <v>37.8452547701464</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -6020,19 +5858,19 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>9.345930521434173</v>
       </c>
       <c r="M56" t="n">
-        <v>9.345930521434173</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>4.839194406156778</v>
       </c>
       <c r="P56" t="n">
-        <v>4.839194406156778</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -6041,62 +5879,59 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>0.01755786066840242</v>
       </c>
       <c r="T56" t="n">
-        <v>0.01755786066840242</v>
+        <v>1853.44487441358</v>
       </c>
       <c r="U56" t="n">
-        <v>1853.44487441358</v>
+        <v>168.4388771926217</v>
       </c>
       <c r="V56" t="n">
-        <v>168.4388771926217</v>
+        <v>-6.580870574065616</v>
       </c>
       <c r="W56" t="n">
-        <v>-6.580870574065616</v>
+        <v>3.290003139873237</v>
       </c>
       <c r="X56" t="n">
-        <v>3.290003139873237</v>
+        <v>0.09668168763662011</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.09668168763662011</v>
+        <v>8.265080646042307</v>
       </c>
       <c r="Z56" t="n">
-        <v>8.265080646042307</v>
+        <v>1.656063968330844</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.656063968330844</v>
+        <v>11.66069329849965</v>
       </c>
       <c r="AB56" t="n">
-        <v>11.66069331397244</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0.002937058651827806</v>
-      </c>
-      <c r="AD56" t="inlineStr">
+        <v>0.002937058674550075</v>
+      </c>
+      <c r="AC56" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD56" t="n">
+        <v>1.645512223243713</v>
+      </c>
       <c r="AE56" t="n">
-        <v>0.4606584012508392</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>7.443541526794434</v>
+        <v>7.149901390075684</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>735</v>
+      <c r="A57" t="n">
+        <v>36.03490394546852</v>
       </c>
       <c r="B57" t="n">
-        <v>36.03490394546852</v>
+        <v>9.599410586395605</v>
       </c>
       <c r="C57" t="n">
-        <v>9.599410586395605</v>
+        <v>34.0855927676545</v>
       </c>
       <c r="D57" t="n">
-        <v>34.0855927676545</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -6120,19 +5955,19 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>13.87879910761875</v>
       </c>
       <c r="M57" t="n">
-        <v>13.87879910761875</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>6.401293592862622</v>
       </c>
       <c r="P57" t="n">
-        <v>6.401293592862622</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -6141,62 +5976,59 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>0.02057324753993761</v>
       </c>
       <c r="T57" t="n">
-        <v>0.02057324753993761</v>
+        <v>1876.078506741097</v>
       </c>
       <c r="U57" t="n">
-        <v>1876.078506741097</v>
+        <v>182.160898661698</v>
       </c>
       <c r="V57" t="n">
-        <v>182.160898661698</v>
+        <v>-7.928390226228701</v>
       </c>
       <c r="W57" t="n">
-        <v>-7.928390226228701</v>
+        <v>3.772239757434389</v>
       </c>
       <c r="X57" t="n">
-        <v>3.772239757434389</v>
+        <v>0.104529959423726</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.104529959423726</v>
+        <v>8.046627103903885</v>
       </c>
       <c r="Z57" t="n">
-        <v>8.046627103903885</v>
+        <v>1.770783550118297</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.770783550118297</v>
+        <v>13.77458170854151</v>
       </c>
       <c r="AB57" t="n">
-        <v>13.77458171938564</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>0.001020675251246272</v>
-      </c>
-      <c r="AD57" t="inlineStr">
+        <v>0.001020675256780401</v>
+      </c>
+      <c r="AC57" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD57" t="n">
+        <v>2.168070077896118</v>
+      </c>
       <c r="AE57" t="n">
-        <v>0.9077197313308716</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>7.842592716217041</v>
+        <v>7.593502998352051</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>736</v>
+      <c r="A58" t="n">
+        <v>33.0417017672229</v>
       </c>
       <c r="B58" t="n">
-        <v>33.0417017672229</v>
+        <v>9.210570393729387</v>
       </c>
       <c r="C58" t="n">
-        <v>9.210570393729387</v>
+        <v>30.17438283411464</v>
       </c>
       <c r="D58" t="n">
-        <v>30.17438283411464</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -6220,19 +6052,19 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>19.9404856197561</v>
       </c>
       <c r="M58" t="n">
-        <v>19.9404856197561</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>7.632859385176974</v>
       </c>
       <c r="P58" t="n">
-        <v>7.632859385176974</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -6241,62 +6073,59 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>0.02343822468082491</v>
       </c>
       <c r="T58" t="n">
-        <v>0.02343822468082491</v>
+        <v>1901.216516047982</v>
       </c>
       <c r="U58" t="n">
-        <v>1901.216516047982</v>
+        <v>193.2800712147922</v>
       </c>
       <c r="V58" t="n">
-        <v>193.2800712147922</v>
+        <v>-9.356054516221842</v>
       </c>
       <c r="W58" t="n">
-        <v>-9.356054516221842</v>
+        <v>4.19591724725608</v>
       </c>
       <c r="X58" t="n">
-        <v>4.19591724725608</v>
+        <v>0.111290116753855</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.111290116753855</v>
+        <v>7.794409896784925</v>
       </c>
       <c r="Z58" t="n">
-        <v>7.794409896784925</v>
+        <v>1.874919214437808</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.874919214437808</v>
+        <v>21.18324278757106</v>
       </c>
       <c r="AB58" t="n">
-        <v>21.18324279697933</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>2.512564805989825e-05</v>
-      </c>
-      <c r="AD58" t="inlineStr">
+        <v>2.512564817802598e-05</v>
+      </c>
+      <c r="AC58" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD58" t="n">
+        <v>2.385072231292725</v>
+      </c>
       <c r="AE58" t="n">
-        <v>0.9457850456237793</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>8.164846420288086</v>
+        <v>7.698232650756836</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>737</v>
+      <c r="A59" t="n">
+        <v>43.98768298598323</v>
       </c>
       <c r="B59" t="n">
-        <v>43.98768298598323</v>
+        <v>4.861815003956776</v>
       </c>
       <c r="C59" t="n">
-        <v>4.861815003956776</v>
+        <v>48.80542061907139</v>
       </c>
       <c r="D59" t="n">
-        <v>48.80542061907139</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -6320,19 +6149,19 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.197504012874014</v>
       </c>
       <c r="M59" t="n">
-        <v>1.197504012874014</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>1.147577378114605</v>
       </c>
       <c r="P59" t="n">
-        <v>1.147577378114605</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -6341,62 +6170,59 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>0.007020681420399731</v>
       </c>
       <c r="T59" t="n">
-        <v>0.007020681420399731</v>
+        <v>1795.845093220265</v>
       </c>
       <c r="U59" t="n">
-        <v>1795.845093220265</v>
+        <v>110.2634744151601</v>
       </c>
       <c r="V59" t="n">
-        <v>110.2634744151601</v>
+        <v>-3.169877969441686</v>
       </c>
       <c r="W59" t="n">
-        <v>-3.169877969441686</v>
+        <v>1.533346063754177</v>
       </c>
       <c r="X59" t="n">
-        <v>1.533346063754177</v>
+        <v>0.06648338701479102</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.06648338701479102</v>
+        <v>8.811654728110417</v>
       </c>
       <c r="Z59" t="n">
-        <v>8.811654728110417</v>
+        <v>1.257111884835559</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.257111884835559</v>
+        <v>20.6956223840143</v>
       </c>
       <c r="AB59" t="n">
-        <v>20.69562240512358</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>3.206289220603065e-05</v>
-      </c>
-      <c r="AD59" t="inlineStr">
+        <v>3.206289254442662e-05</v>
+      </c>
+      <c r="AC59" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD59" t="n">
+        <v>0.3697644770145416</v>
+      </c>
       <c r="AE59" t="n">
-        <v>-0.5934247970581055</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>6.290301322937012</v>
+        <v>6.4790358543396</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>738</v>
+      <c r="A60" t="n">
+        <v>45.7006317110727</v>
       </c>
       <c r="B60" t="n">
-        <v>45.7006317110727</v>
+        <v>5.261669557711915</v>
       </c>
       <c r="C60" t="n">
-        <v>5.261669557711915</v>
+        <v>45.86244388137209</v>
       </c>
       <c r="D60" t="n">
-        <v>45.86244388137209</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -6420,19 +6246,19 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.775096118004433</v>
       </c>
       <c r="M60" t="n">
-        <v>1.775096118004433</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>1.400158731838864</v>
       </c>
       <c r="P60" t="n">
-        <v>1.400158731838864</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -6441,62 +6267,59 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>0.008384986032816942</v>
       </c>
       <c r="T60" t="n">
-        <v>0.008384986032816942</v>
+        <v>1802.148573118088</v>
       </c>
       <c r="U60" t="n">
-        <v>1802.148573118088</v>
+        <v>116.5216306197396</v>
       </c>
       <c r="V60" t="n">
-        <v>116.5216306197396</v>
+        <v>-3.427202865796386</v>
       </c>
       <c r="W60" t="n">
-        <v>-3.427202865796386</v>
+        <v>1.740534888920838</v>
       </c>
       <c r="X60" t="n">
-        <v>1.740534888920838</v>
+        <v>0.06946583971910668</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.06946583971910668</v>
+        <v>8.727249723932941</v>
       </c>
       <c r="Z60" t="n">
-        <v>8.727249723932941</v>
+        <v>1.291995277657361</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.291995277657361</v>
+        <v>20.47257731893701</v>
       </c>
       <c r="AB60" t="n">
-        <v>20.47257734258948</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>3.58456380239458e-05</v>
-      </c>
-      <c r="AD60" t="inlineStr">
+        <v>3.584563844782895e-05</v>
+      </c>
+      <c r="AC60" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD60" t="n">
+        <v>0.409483402967453</v>
+      </c>
       <c r="AE60" t="n">
-        <v>-0.4416285753250122</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>6.434042930603027</v>
+        <v>6.404086589813232</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>739</v>
+      <c r="A61" t="n">
+        <v>46.67965674781412</v>
       </c>
       <c r="B61" t="n">
-        <v>46.67965674781412</v>
+        <v>5.9600395804174</v>
       </c>
       <c r="C61" t="n">
-        <v>5.9600395804174</v>
+        <v>42.95387824215434</v>
       </c>
       <c r="D61" t="n">
-        <v>42.95387824215434</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -6520,19 +6343,19 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.650078640641265</v>
       </c>
       <c r="M61" t="n">
-        <v>2.650078640641265</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>1.756346788972866</v>
       </c>
       <c r="P61" t="n">
-        <v>1.756346788972866</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -6541,62 +6364,59 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>0.01006730639377948</v>
       </c>
       <c r="T61" t="n">
-        <v>0.01006730639377948</v>
+        <v>1810.787089402293</v>
       </c>
       <c r="U61" t="n">
-        <v>1810.787089402293</v>
+        <v>125.7638995629434</v>
       </c>
       <c r="V61" t="n">
-        <v>125.7638995629434</v>
+        <v>-3.815018955229054</v>
       </c>
       <c r="W61" t="n">
-        <v>-3.815018955229054</v>
+        <v>1.99785389706251</v>
       </c>
       <c r="X61" t="n">
-        <v>1.99785389706251</v>
+        <v>0.07390825546166216</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.07390825546166216</v>
+        <v>8.628153340593789</v>
       </c>
       <c r="Z61" t="n">
-        <v>8.628153340593789</v>
+        <v>1.344226957979696</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.344226957979696</v>
+        <v>19.80158102680508</v>
       </c>
       <c r="AB61" t="n">
-        <v>19.80158104685045</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>5.01350334682904e-05</v>
-      </c>
-      <c r="AD61" t="inlineStr">
+        <v>5.013503397077734e-05</v>
+      </c>
+      <c r="AC61" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD61" t="n">
+        <v>0.5787966847419739</v>
+      </c>
       <c r="AE61" t="n">
-        <v>-0.3479690849781036</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>6.542584419250488</v>
+        <v>6.52287769317627</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>740</v>
+      <c r="A62" t="n">
+        <v>47.53914448671719</v>
       </c>
       <c r="B62" t="n">
-        <v>47.53914448671719</v>
+        <v>6.459960652427106</v>
       </c>
       <c r="C62" t="n">
-        <v>6.459960652427106</v>
+        <v>39.99189540478646</v>
       </c>
       <c r="D62" t="n">
-        <v>39.99189540478646</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -6620,19 +6440,19 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>3.714419367589803</v>
       </c>
       <c r="M62" t="n">
-        <v>3.714419367589803</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>2.294580088479436</v>
       </c>
       <c r="P62" t="n">
-        <v>2.294580088479436</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -6641,62 +6461,59 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>0.01174873452414173</v>
       </c>
       <c r="T62" t="n">
-        <v>0.01174873452414173</v>
+        <v>1819.333862307396</v>
       </c>
       <c r="U62" t="n">
-        <v>1819.333862307396</v>
+        <v>133.768939192973</v>
       </c>
       <c r="V62" t="n">
-        <v>133.768939192973</v>
+        <v>-4.216226695607757</v>
       </c>
       <c r="W62" t="n">
-        <v>-4.216226695607757</v>
+        <v>2.236641780729235</v>
       </c>
       <c r="X62" t="n">
-        <v>2.236641780729235</v>
+        <v>0.07785768910493723</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.07785768910493723</v>
+        <v>8.528321940023906</v>
       </c>
       <c r="Z62" t="n">
-        <v>8.528321940023906</v>
+        <v>1.39133283844068</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.39133283844068</v>
+        <v>19.73262869906821</v>
       </c>
       <c r="AB62" t="n">
-        <v>19.73262872526005</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>5.189363771795907e-05</v>
-      </c>
-      <c r="AD62" t="inlineStr">
+        <v>5.189363839752659e-05</v>
+      </c>
+      <c r="AC62" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD62" t="n">
+        <v>0.809961199760437</v>
+      </c>
       <c r="AE62" t="n">
-        <v>-0.3353989720344543</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>6.836453437805176</v>
+        <v>6.645302295684814</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>741</v>
+      <c r="A63" t="n">
+        <v>47.07121651777462</v>
       </c>
       <c r="B63" t="n">
-        <v>47.07121651777462</v>
+        <v>6.707840058122374</v>
       </c>
       <c r="C63" t="n">
-        <v>6.707840058122374</v>
+        <v>37.18219308233689</v>
       </c>
       <c r="D63" t="n">
-        <v>37.18219308233689</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -6720,19 +6537,19 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>5.911898848075174</v>
       </c>
       <c r="M63" t="n">
-        <v>5.911898848075174</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.126851493690946</v>
       </c>
       <c r="P63" t="n">
-        <v>3.126851493690946</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -6741,62 +6558,59 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>0.0144858494561258</v>
       </c>
       <c r="T63" t="n">
-        <v>0.0144858494561258</v>
+        <v>1831.237971787176</v>
       </c>
       <c r="U63" t="n">
-        <v>1831.237971787176</v>
+        <v>145.1006768504383</v>
       </c>
       <c r="V63" t="n">
-        <v>145.1006768504383</v>
+        <v>-5.011414499462786</v>
       </c>
       <c r="W63" t="n">
-        <v>-5.011414499462786</v>
+        <v>2.637752997236562</v>
       </c>
       <c r="X63" t="n">
-        <v>2.637752997236562</v>
+        <v>0.08399553639921081</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.08399553639921081</v>
+        <v>8.402305735263715</v>
       </c>
       <c r="Z63" t="n">
-        <v>8.402305735263715</v>
+        <v>1.47494070944119</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.47494070944119</v>
+        <v>18.61404592161488</v>
       </c>
       <c r="AB63" t="n">
-        <v>18.61404594072812</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>9.078441115928371e-05</v>
-      </c>
-      <c r="AD63" t="inlineStr">
+        <v>9.0784412026923e-05</v>
+      </c>
+      <c r="AC63" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD63" t="n">
+        <v>1.111826777458191</v>
+      </c>
       <c r="AE63" t="n">
-        <v>-0.01832944341003895</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>7.114097595214844</v>
+        <v>6.92650318145752</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>742</v>
+      <c r="A64" t="n">
+        <v>45.67156598130153</v>
       </c>
       <c r="B64" t="n">
-        <v>45.67156598130153</v>
+        <v>7.420825315198804</v>
       </c>
       <c r="C64" t="n">
-        <v>7.420825315198804</v>
+        <v>34.1968373589592</v>
       </c>
       <c r="D64" t="n">
-        <v>34.1968373589592</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -6820,19 +6634,19 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>8.668102187239116</v>
       </c>
       <c r="M64" t="n">
-        <v>8.668102187239116</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>4.042669157301349</v>
       </c>
       <c r="P64" t="n">
-        <v>4.042669157301349</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -6841,62 +6655,59 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>0.0171057748099153</v>
       </c>
       <c r="T64" t="n">
-        <v>0.0171057748099153</v>
+        <v>1847.282242523307</v>
       </c>
       <c r="U64" t="n">
-        <v>1847.282242523307</v>
+        <v>158.5146067313444</v>
       </c>
       <c r="V64" t="n">
-        <v>158.5146067313444</v>
+        <v>-5.942931048174591</v>
       </c>
       <c r="W64" t="n">
-        <v>-5.942931048174591</v>
+        <v>3.015554825671705</v>
       </c>
       <c r="X64" t="n">
-        <v>3.015554825671705</v>
+        <v>0.09111327542057475</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.09111327542057475</v>
+        <v>8.245782027590725</v>
       </c>
       <c r="Z64" t="n">
-        <v>8.245782027590725</v>
+        <v>1.57026622705338</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.57026622705338</v>
+        <v>17.86713724361446</v>
       </c>
       <c r="AB64" t="n">
-        <v>17.8671372573849</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>0.0001318865296813243</v>
-      </c>
-      <c r="AD64" t="inlineStr">
+        <v>0.0001318865305893757</v>
+      </c>
+      <c r="AC64" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD64" t="n">
+        <v>1.494933724403381</v>
+      </c>
       <c r="AE64" t="n">
-        <v>0.3254123628139496</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>7.335958480834961</v>
+        <v>7.162810325622559</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>743</v>
+      <c r="A65" t="n">
+        <v>42.51104340916319</v>
       </c>
       <c r="B65" t="n">
-        <v>42.51104340916319</v>
+        <v>7.292241982690449</v>
       </c>
       <c r="C65" t="n">
-        <v>7.292241982690449</v>
+        <v>31.85374036730268</v>
       </c>
       <c r="D65" t="n">
-        <v>31.85374036730268</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -6920,19 +6731,19 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>13.13901354135515</v>
       </c>
       <c r="M65" t="n">
-        <v>13.13901354135515</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>5.203960699488528</v>
       </c>
       <c r="P65" t="n">
-        <v>5.203960699488528</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -6941,62 +6752,59 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>0.02028029107249054</v>
       </c>
       <c r="T65" t="n">
-        <v>0.02028029107249054</v>
+        <v>1866.213199387029</v>
       </c>
       <c r="U65" t="n">
-        <v>1866.213199387029</v>
+        <v>172.428688213657</v>
       </c>
       <c r="V65" t="n">
-        <v>172.428688213657</v>
+        <v>-7.32186796334867</v>
       </c>
       <c r="W65" t="n">
-        <v>-7.32186796334867</v>
+        <v>3.505362499811748</v>
       </c>
       <c r="X65" t="n">
-        <v>3.505362499811748</v>
+        <v>0.09925616978069154</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.09925616978069154</v>
+        <v>8.066734709252797</v>
       </c>
       <c r="Z65" t="n">
-        <v>8.066734709252797</v>
+        <v>1.693277583234823</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.693277583234823</v>
+        <v>18.04414051397846</v>
       </c>
       <c r="AB65" t="n">
-        <v>18.04414053114573</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>0.0001207159532837787</v>
-      </c>
-      <c r="AD65" t="inlineStr">
+        <v>0.0001207159543199499</v>
+      </c>
+      <c r="AC65" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD65" t="n">
+        <v>1.934536695480347</v>
+      </c>
       <c r="AE65" t="n">
-        <v>0.7341803312301636</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>7.71480131149292</v>
+        <v>7.480154991149902</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>744</v>
+      <c r="A66" t="n">
+        <v>54.37577254606605</v>
       </c>
       <c r="B66" t="n">
-        <v>54.37577254606605</v>
+        <v>4.163980532700686</v>
       </c>
       <c r="C66" t="n">
-        <v>4.163980532700686</v>
+        <v>38.51361416459901</v>
       </c>
       <c r="D66" t="n">
-        <v>38.51361416459901</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -7020,19 +6828,19 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.626418744769528</v>
       </c>
       <c r="M66" t="n">
-        <v>1.626418744769528</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>1.320214011864745</v>
       </c>
       <c r="P66" t="n">
-        <v>1.320214011864745</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -7041,62 +6849,59 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>0.008094941929136089</v>
       </c>
       <c r="T66" t="n">
-        <v>0.008094941929136089</v>
+        <v>1803.065062095973</v>
       </c>
       <c r="U66" t="n">
-        <v>1803.065062095973</v>
+        <v>105.865055616446</v>
       </c>
       <c r="V66" t="n">
-        <v>105.865055616446</v>
+        <v>-3.035920942155328</v>
       </c>
       <c r="W66" t="n">
-        <v>-3.035920942155328</v>
+        <v>1.534616405860436</v>
       </c>
       <c r="X66" t="n">
-        <v>1.534616405860436</v>
+        <v>0.06391158313549025</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.06391158313549025</v>
+        <v>8.611481637450535</v>
       </c>
       <c r="Z66" t="n">
-        <v>8.611481637450535</v>
+        <v>1.212817224831085</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.212817224831085</v>
+        <v>32.00728390390313</v>
       </c>
       <c r="AB66" t="n">
-        <v>32.00728393377128</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>1.121260707614979e-07</v>
-      </c>
-      <c r="AD66" t="inlineStr">
+        <v>1.121260724268325e-07</v>
+      </c>
+      <c r="AC66" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD66" t="n">
+        <v>0.4242263734340668</v>
+      </c>
       <c r="AE66" t="n">
-        <v>-0.4169232547283173</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>6.666397094726562</v>
+        <v>6.703407287597656</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>745</v>
+      <c r="A67" t="n">
+        <v>55.07062752917076</v>
       </c>
       <c r="B67" t="n">
-        <v>55.07062752917076</v>
+        <v>4.548597416346031</v>
       </c>
       <c r="C67" t="n">
-        <v>4.548597416346031</v>
+        <v>36.40809164276832</v>
       </c>
       <c r="D67" t="n">
-        <v>36.40809164276832</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -7120,19 +6925,19 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.493750665872093</v>
       </c>
       <c r="M67" t="n">
-        <v>2.493750665872093</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>1.478932745842804</v>
       </c>
       <c r="P67" t="n">
-        <v>1.478932745842804</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7141,62 +6946,59 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>0.009835056787021469</v>
       </c>
       <c r="T67" t="n">
-        <v>0.009835056787021469</v>
+        <v>1809.826507441956</v>
       </c>
       <c r="U67" t="n">
-        <v>1809.826507441956</v>
+        <v>114.0652537013903</v>
       </c>
       <c r="V67" t="n">
-        <v>114.0652537013903</v>
+        <v>-3.369887366306302</v>
       </c>
       <c r="W67" t="n">
-        <v>-3.369887366306302</v>
+        <v>1.783872531566455</v>
       </c>
       <c r="X67" t="n">
-        <v>1.783872531566455</v>
+        <v>0.06781306660551203</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.06781306660551203</v>
+        <v>8.533890670384872</v>
       </c>
       <c r="Z67" t="n">
-        <v>8.533890670384872</v>
+        <v>1.256868418005553</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.256868418005553</v>
+        <v>32.01610748072851</v>
       </c>
       <c r="AB67" t="n">
-        <v>32.01610751310999</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>1.116324837013849e-07</v>
-      </c>
-      <c r="AD67" t="inlineStr">
+        <v>1.116324854777417e-07</v>
+      </c>
+      <c r="AC67" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD67" t="n">
+        <v>0.5567468404769897</v>
+      </c>
       <c r="AE67" t="n">
-        <v>-0.3251573741436005</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>6.767315864562988</v>
+        <v>6.699188709259033</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>746</v>
+      <c r="A68" t="n">
+        <v>54.82432856758766</v>
       </c>
       <c r="B68" t="n">
-        <v>54.82432856758766</v>
+        <v>4.911082626026415</v>
       </c>
       <c r="C68" t="n">
-        <v>4.911082626026415</v>
+        <v>34.63480630646283</v>
       </c>
       <c r="D68" t="n">
-        <v>34.63480630646283</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -7220,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.655998540179822</v>
       </c>
       <c r="M68" t="n">
-        <v>3.655998540179822</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>1.973783959743264</v>
       </c>
       <c r="P68" t="n">
-        <v>1.973783959743264</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -7241,62 +7043,59 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>0.01171591481623785</v>
       </c>
       <c r="T68" t="n">
-        <v>0.01171591481623785</v>
+        <v>1817.28357425396</v>
       </c>
       <c r="U68" t="n">
-        <v>1817.28357425396</v>
+        <v>123.1094484623871</v>
       </c>
       <c r="V68" t="n">
-        <v>123.1094484623871</v>
+        <v>-3.81061272426053</v>
       </c>
       <c r="W68" t="n">
-        <v>-3.81061272426053</v>
+        <v>2.055573873248151</v>
       </c>
       <c r="X68" t="n">
-        <v>2.055573873248151</v>
+        <v>0.07233037751903099</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.07233037751903099</v>
+        <v>8.456941706699954</v>
       </c>
       <c r="Z68" t="n">
-        <v>8.456941706699954</v>
+        <v>1.311634526868541</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.311634526868541</v>
+        <v>30.78921585778702</v>
       </c>
       <c r="AB68" t="n">
-        <v>30.78921589133044</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>2.061610977488471e-07</v>
-      </c>
-      <c r="AD68" t="inlineStr">
+        <v>2.061611013015607e-07</v>
+      </c>
+      <c r="AC68" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD68" t="n">
+        <v>0.771543562412262</v>
+      </c>
       <c r="AE68" t="n">
-        <v>-0.2683905065059662</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>6.952888011932373</v>
+        <v>6.888813972473145</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
-        <v>747</v>
+      <c r="A69" t="n">
+        <v>54.18769809434324</v>
       </c>
       <c r="B69" t="n">
-        <v>54.18769809434324</v>
+        <v>5.396440362725046</v>
       </c>
       <c r="C69" t="n">
-        <v>5.396440362725046</v>
+        <v>32.54375236898584</v>
       </c>
       <c r="D69" t="n">
-        <v>32.54375236898584</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -7320,19 +7119,19 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>5.431837183713921</v>
       </c>
       <c r="M69" t="n">
-        <v>5.431837183713921</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>2.440271990231944</v>
       </c>
       <c r="P69" t="n">
-        <v>2.440271990231944</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -7341,62 +7140,59 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>0.01401347287902438</v>
       </c>
       <c r="T69" t="n">
-        <v>0.01401347287902438</v>
+        <v>1827.976410804391</v>
       </c>
       <c r="U69" t="n">
-        <v>1827.976410804391</v>
+        <v>134.7759155198548</v>
       </c>
       <c r="V69" t="n">
-        <v>134.7759155198548</v>
+        <v>-4.447296024796836</v>
       </c>
       <c r="W69" t="n">
-        <v>-4.447296024796836</v>
+        <v>2.370016088240881</v>
       </c>
       <c r="X69" t="n">
-        <v>2.370016088240881</v>
+        <v>0.07827521299886665</v>
       </c>
       <c r="Y69" t="n">
-        <v>0.07827521299886665</v>
+        <v>8.350610399426499</v>
       </c>
       <c r="Z69" t="n">
-        <v>8.350610399426499</v>
+        <v>1.386573576065322</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.386573576065322</v>
+        <v>29.40591279513523</v>
       </c>
       <c r="AB69" t="n">
-        <v>29.40591282370115</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>4.117059682062774e-07</v>
-      </c>
-      <c r="AD69" t="inlineStr">
+        <v>4.117059740904594e-07</v>
+      </c>
+      <c r="AC69" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD69" t="n">
+        <v>0.9418314099311829</v>
+      </c>
       <c r="AE69" t="n">
-        <v>-0.1885654330253601</v>
-      </c>
-      <c r="AF69" t="n">
-        <v>7.007810115814209</v>
+        <v>6.859591484069824</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
-        <v>748</v>
+      <c r="A70" t="n">
+        <v>51.347187815424</v>
       </c>
       <c r="B70" t="n">
-        <v>51.347187815424</v>
+        <v>5.827792524021215</v>
       </c>
       <c r="C70" t="n">
-        <v>5.827792524021215</v>
+        <v>31.58485426038688</v>
       </c>
       <c r="D70" t="n">
-        <v>31.58485426038688</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -7420,19 +7216,19 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>8.142295094829825</v>
       </c>
       <c r="M70" t="n">
-        <v>8.142295094829825</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.097870305338082</v>
       </c>
       <c r="P70" t="n">
-        <v>3.097870305338082</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -7441,48 +7237,45 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>0.01673090512309462</v>
       </c>
       <c r="T70" t="n">
-        <v>0.01673090512309462</v>
+        <v>1841.240482974366</v>
       </c>
       <c r="U70" t="n">
-        <v>1841.240482974366</v>
+        <v>148.9821337428867</v>
       </c>
       <c r="V70" t="n">
-        <v>148.9821337428867</v>
+        <v>-5.43757601361474</v>
       </c>
       <c r="W70" t="n">
-        <v>-5.43757601361474</v>
+        <v>2.782294078387221</v>
       </c>
       <c r="X70" t="n">
-        <v>2.782294078387221</v>
+        <v>0.08603840074667479</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.08603840074667479</v>
+        <v>8.238582347543927</v>
       </c>
       <c r="Z70" t="n">
-        <v>8.238582347543927</v>
+        <v>1.496411259435297</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.496411259435297</v>
+        <v>25.46340519572347</v>
       </c>
       <c r="AB70" t="n">
-        <v>25.46340521749815</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>2.955914118030201e-06</v>
-      </c>
-      <c r="AD70" t="inlineStr">
+        <v>2.955914150226668e-06</v>
+      </c>
+      <c r="AC70" t="inlineStr">
         <is>
           <t>new NiCrCoVFe data</t>
         </is>
       </c>
+      <c r="AD70" t="n">
+        <v>1.256969571113586</v>
+      </c>
       <c r="AE70" t="n">
-        <v>0.1985452771186829</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>7.339662551879883</v>
+        <v>7.149888515472412</v>
       </c>
     </row>
   </sheetData>
